--- a/public/downloads/FantaQMCcopperCO2024.xlsx
+++ b/public/downloads/FantaQMCcopperCO2024.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="59">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CO</t>
@@ -671,10 +694,10 @@
         <v>156</v>
       </c>
       <c r="N3" s="5">
-        <v>359.0904123783112</v>
+        <v>359090.4123783112</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03250569497404826</v>
+        <v>32.50569497404826</v>
       </c>
       <c r="P3" s="5">
         <v>11047</v>
@@ -721,10 +744,10 @@
         <v>156</v>
       </c>
       <c r="N4" s="5">
-        <v>810.6599159240723</v>
+        <v>810659.9159240723</v>
       </c>
       <c r="O4" s="4">
-        <v>0.0456093122495821</v>
+        <v>45.6093122495821</v>
       </c>
       <c r="P4" s="5">
         <v>17774</v>
@@ -771,10 +794,10 @@
         <v>156</v>
       </c>
       <c r="N5" s="5">
-        <v>2296.41382598877</v>
+        <v>2296413.82598877</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1431054917423051</v>
+        <v>143.1054917423051</v>
       </c>
       <c r="P5" s="5">
         <v>16047</v>
@@ -821,10 +844,10 @@
         <v>156</v>
       </c>
       <c r="N6" s="5">
-        <v>1481.218880176544</v>
+        <v>1481218.880176544</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08422237335398557</v>
+        <v>84.22237335398556</v>
       </c>
       <c r="P6" s="5">
         <v>17587</v>
@@ -871,10 +894,10 @@
         <v>156</v>
       </c>
       <c r="N7" s="5">
-        <v>1644.88089799881</v>
+        <v>1644880.89799881</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1722208038947555</v>
+        <v>172.2208038947555</v>
       </c>
       <c r="P7" s="5">
         <v>9551</v>
@@ -921,10 +944,10 @@
         <v>156</v>
       </c>
       <c r="N8" s="5">
-        <v>211.1189484596252</v>
+        <v>211118.9484596252</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01278269244730112</v>
+        <v>12.78269244730112</v>
       </c>
       <c r="P8" s="5">
         <v>16516</v>
@@ -971,10 +994,10 @@
         <v>156</v>
       </c>
       <c r="N9" s="5">
-        <v>550.8222744464874</v>
+        <v>550822.2744464874</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02985810247433258</v>
+        <v>29.85810247433258</v>
       </c>
       <c r="P9" s="5">
         <v>18448</v>
@@ -1021,10 +1044,10 @@
         <v>156</v>
       </c>
       <c r="N10" s="5">
-        <v>981.849686384201</v>
+        <v>981849.686384201</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1012320534471802</v>
+        <v>101.2320534471802</v>
       </c>
       <c r="P10" s="5">
         <v>9699</v>
@@ -1071,10 +1094,10 @@
         <v>156</v>
       </c>
       <c r="N11" s="5">
-        <v>622.1174757480621</v>
+        <v>622117.4757480621</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03993820862477127</v>
+        <v>39.93820862477127</v>
       </c>
       <c r="P11" s="5">
         <v>15577</v>
@@ -1121,10 +1144,10 @@
         <v>156</v>
       </c>
       <c r="N12" s="5">
-        <v>258.2798476219177</v>
+        <v>258279.8476219177</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01908941963207078</v>
+        <v>19.08941963207078</v>
       </c>
       <c r="P12" s="5">
         <v>13530</v>
@@ -1171,10 +1194,10 @@
         <v>156</v>
       </c>
       <c r="N13" s="5">
-        <v>768.0313620567322</v>
+        <v>768031.3620567322</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07714256348500725</v>
+        <v>77.14256348500726</v>
       </c>
       <c r="P13" s="5">
         <v>9956</v>
@@ -1221,10 +1244,10 @@
         <v>128</v>
       </c>
       <c r="N14" s="5">
-        <v>2749.436969041824</v>
+        <v>2749436.969041824</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2356189021374432</v>
+        <v>235.6189021374432</v>
       </c>
       <c r="P14" s="5">
         <v>11669</v>
@@ -1271,10 +1294,10 @@
         <v>128</v>
       </c>
       <c r="N15" s="5">
-        <v>2227.689119577408</v>
+        <v>2227689.119577408</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2424036038713175</v>
+        <v>242.4036038713175</v>
       </c>
       <c r="P15" s="5">
         <v>9190</v>
@@ -1321,10 +1344,10 @@
         <v>128</v>
       </c>
       <c r="N16" s="5">
-        <v>1103.922834396362</v>
+        <v>1103922.834396362</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09400688362397704</v>
+        <v>94.00688362397703</v>
       </c>
       <c r="P16" s="5">
         <v>11743</v>
@@ -1371,10 +1394,10 @@
         <v>128</v>
       </c>
       <c r="N17" s="5">
-        <v>943.1171712875366</v>
+        <v>943117.1712875366</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1053644476916028</v>
+        <v>105.3644476916028</v>
       </c>
       <c r="P17" s="5">
         <v>8951</v>
@@ -1402,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1413,9 +1436,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1449,8 +1478,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1472,119 +1509,173 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.507077322885656</v>
+        <v>1.149870972698643</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3706239953972305</v>
+        <v>0.8246028319952297</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5064408463420628</v>
+        <v>1.136932554722177</v>
       </c>
       <c r="E3" s="4">
-        <v>95.88520408163265</v>
+        <v>94.67602040816327</v>
       </c>
       <c r="F3" s="4">
-        <v>97.51174496644295</v>
+        <v>96.57298657718121</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
       </c>
       <c r="H3" s="5">
+        <v>36</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.149870972698643</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7871002672722581</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5779316120488628</v>
+      </c>
+      <c r="R3" s="5">
         <v>37</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="S3" s="5">
         <v>3</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.182424335327104</v>
+        <v>2.670330691312031</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6277799160391252</v>
+        <v>1.085743198894969</v>
       </c>
       <c r="D4" s="4">
-        <v>1.085202052426171</v>
+        <v>2.125306840314905</v>
       </c>
       <c r="E4" s="4">
-        <v>87.98833819242017</v>
+        <v>77.9421768707479</v>
       </c>
       <c r="F4" s="4">
-        <v>90.05992329817749</v>
+        <v>79.65484180249257</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
+        <v>12</v>
+      </c>
+      <c r="J4" s="5">
+        <v>8</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
         <v>7</v>
       </c>
-      <c r="J4" s="5">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-2.172882659272688</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.419460870467524</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7095762312878977</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3804167156309445</v>
+        <v>1.28125693655206</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2662192148058027</v>
+        <v>0.4727303005313027</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2583738927069349</v>
+        <v>1.208653347729461</v>
       </c>
       <c r="E5" s="4">
-        <v>89.04458211856162</v>
+        <v>90.54664723032076</v>
       </c>
       <c r="F5" s="4">
-        <v>85.54370405880432</v>
+        <v>89.14789069990286</v>
       </c>
       <c r="G5" s="5">
         <v>56</v>
       </c>
       <c r="H5" s="5">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I5" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -1593,68 +1684,104 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-1.13729352910163</v>
+      </c>
+      <c r="O5" s="5">
+        <v>46</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.060600583422991</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8753370723954619</v>
+      </c>
+      <c r="R5" s="5">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.8720329675280035</v>
+        <v>1.931029961421386</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4310942811149855</v>
+        <v>1.090191500168673</v>
       </c>
       <c r="D6" s="4">
-        <v>0.8487688410685733</v>
+        <v>1.849495096907873</v>
       </c>
       <c r="E6" s="4">
-        <v>89.18792517006796</v>
+        <v>85.45918367346938</v>
       </c>
       <c r="F6" s="4">
-        <v>91.45274049216955</v>
+        <v>86.41918344518992</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I6" s="5">
         <v>1</v>
       </c>
       <c r="J6" s="5">
+        <v>7</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>7</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-1.939510650697573</v>
+      </c>
+      <c r="O6" s="5">
+        <v>23</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.145208414772707</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7387249399058962</v>
+      </c>
+      <c r="R6" s="5">
+        <v>19</v>
+      </c>
+      <c r="S6" s="5">
         <v>4</v>
       </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.112819628983444</v>
+        <v>1.687427134780928</v>
       </c>
       <c r="C7" s="4">
-        <v>1.112819628983444</v>
+        <v>1.687427134780928</v>
       </c>
       <c r="D7" s="4">
-        <v>1.103062413953686</v>
+        <v>1.653930127278302</v>
       </c>
       <c r="E7" s="4">
-        <v>97.37244897959184</v>
+        <v>93.16326530612245</v>
       </c>
       <c r="F7" s="4">
-        <v>98.00335570469798</v>
+        <v>93.35570469798658</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
@@ -1677,25 +1804,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.687427134780928</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.687427134780928</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1850123905568728</v>
+        <v>0.3631239746225166</v>
       </c>
       <c r="C8" s="4">
-        <v>0.1850123905568728</v>
+        <v>0.3631239746225166</v>
       </c>
       <c r="D8" s="4">
-        <v>0.1847726551129016</v>
+        <v>0.3645609420697369</v>
       </c>
       <c r="E8" s="4">
-        <v>99.79591836734694</v>
+        <v>95.40816326530613</v>
       </c>
       <c r="F8" s="4">
-        <v>99.22818791946308</v>
+        <v>97.08053691275168</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -1718,34 +1861,48 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.3631239746225166</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.3631239746225166</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.1158033590079117</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.1158033590079117</v>
-      </c>
+        <v>0.7530025178834512</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
-        <v>0.115815396397444</v>
+        <v>0.5236403675151209</v>
       </c>
       <c r="E9" s="4">
-        <v>99.08163265306122</v>
+        <v>55.30612244897959</v>
       </c>
       <c r="F9" s="4">
-        <v>98.55704697986577</v>
+        <v>48.89261744966443</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -1759,9 +1916,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.7530025178834512</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1772,6 +1943,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1779,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1790,9 +1962,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1826,8 +2004,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1849,122 +2035,176 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5176751686562057</v>
+        <v>1.388262136484264</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3220792214954546</v>
+        <v>1.036059950682517</v>
       </c>
       <c r="D3" s="4">
-        <v>0.51436580609261</v>
+        <v>1.372024972940562</v>
       </c>
       <c r="E3" s="4">
-        <v>93.27721088435374</v>
+        <v>94.13095238095238</v>
       </c>
       <c r="F3" s="4">
-        <v>95.61940715883668</v>
+        <v>96.05816554809844</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
       </c>
       <c r="H3" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.40096893360598</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8597941328300432</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6254460085616417</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.655174946099578</v>
+        <v>3.520654039855539</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6351322109252439</v>
+        <v>1.42583879918493</v>
       </c>
       <c r="D4" s="4">
-        <v>1.160493205745297</v>
+        <v>3.068898584293493</v>
       </c>
       <c r="E4" s="4">
-        <v>79.0427599611273</v>
+        <v>80.50170068027208</v>
       </c>
       <c r="F4" s="4">
-        <v>80.22651006711308</v>
+        <v>82.31743368488327</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
         <v>13</v>
       </c>
-      <c r="I4" s="5">
-        <v>13</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-3.060926337398996</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.660313642044847</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7594021782533673</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5288925792379554</v>
+        <v>0.3345885537234738</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4838013288986581</v>
+        <v>0.3065869533369551</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5002249870342764</v>
+        <v>0.3226438545160428</v>
       </c>
       <c r="E5" s="4">
-        <v>87.66520894071914</v>
+        <v>90.89042759961124</v>
       </c>
       <c r="F5" s="4">
-        <v>83.07086928731083</v>
+        <v>90.91343080856491</v>
       </c>
       <c r="G5" s="5">
         <v>56</v>
       </c>
       <c r="H5" s="5">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="I5" s="5">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1972,37 +2212,55 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.1789593724141014</v>
+      </c>
+      <c r="O5" s="5">
+        <v>50</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3155410502200539</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3029212732286542</v>
+      </c>
+      <c r="R5" s="5">
+        <v>50</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.395430782121972</v>
+        <v>3.400544724055786</v>
       </c>
       <c r="C6" s="4">
-        <v>0.8096344199275336</v>
+        <v>1.533573480327808</v>
       </c>
       <c r="D6" s="4">
-        <v>1.185803948524153</v>
+        <v>3.019866348493755</v>
       </c>
       <c r="E6" s="4">
-        <v>84.12556689342406</v>
+        <v>71.6439909297053</v>
       </c>
       <c r="F6" s="4">
-        <v>84.54651379567515</v>
+        <v>73.19258016405635</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J6" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -2011,39 +2269,55 @@
         <v>0</v>
       </c>
       <c r="M6" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>12</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-3.258119334041839</v>
+      </c>
+      <c r="O6" s="5">
+        <v>15</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.552058691877088</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.8141713764603572</v>
+      </c>
+      <c r="R6" s="5">
+        <v>13</v>
+      </c>
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.455689133075794</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.455689133075794</v>
-      </c>
+        <v>2.422941625980457</v>
+      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4">
-        <v>1.32079166260155</v>
+        <v>2.158248127369006</v>
       </c>
       <c r="E7" s="4">
-        <v>87.60204081632654</v>
+        <v>67.14285714285714</v>
       </c>
       <c r="F7" s="4">
-        <v>88.8758389261745</v>
+        <v>68.93456375838926</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
@@ -2052,36 +2326,48 @@
         <v>0</v>
       </c>
       <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2.422941625980457</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1570611494098557</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.1570611494098557</v>
-      </c>
+        <v>1.423597915811115</v>
+      </c>
+      <c r="C8" s="4"/>
       <c r="D8" s="4">
-        <v>0.1570649641071213</v>
+        <v>1.170272215051227</v>
       </c>
       <c r="E8" s="4">
-        <v>95.30612244897959</v>
+        <v>85.10204081632654</v>
       </c>
       <c r="F8" s="4">
-        <v>97.4496644295302</v>
+        <v>79.83221476510067</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
       </c>
       <c r="H8" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -2095,25 +2381,37 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1.423597915811115</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3062919591611717</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+        <v>1.928359172219643</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
-        <v>0.1225291703885887</v>
+        <v>1.079299828881631</v>
       </c>
       <c r="E9" s="4">
-        <v>61.97278911564625</v>
+        <v>55.90136054421769</v>
       </c>
       <c r="F9" s="4">
-        <v>48.32214765100671</v>
+        <v>53.64653243847874</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -2136,9 +2434,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1.928359172219643</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2149,6 +2461,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2156,7 +2469,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2167,9 +2480,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2203,8 +2522,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2226,37 +2553,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.086917026544688</v>
+        <v>0.507077322885656</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7863394594250066</v>
+        <v>0.3706239953972305</v>
       </c>
       <c r="D3" s="4">
-        <v>1.107068021799205</v>
+        <v>0.5064408463420628</v>
       </c>
       <c r="E3" s="4">
-        <v>93.79506802721089</v>
+        <v>95.88520408163265</v>
       </c>
       <c r="F3" s="4">
-        <v>96.05425055928413</v>
+        <v>97.51174496644295</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
       </c>
       <c r="H3" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -2265,36 +2610,54 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.225104773083747</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5520982775024054</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.513379476452565</v>
+      </c>
+      <c r="R3" s="5">
+        <v>39</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.229741956638463</v>
+        <v>1.182424335327104</v>
       </c>
       <c r="C4" s="4">
-        <v>1.09321489181986</v>
+        <v>0.6277799160391252</v>
       </c>
       <c r="D4" s="4">
-        <v>1.690706159519323</v>
+        <v>1.085202052426171</v>
       </c>
       <c r="E4" s="4">
-        <v>77.48663751214775</v>
+        <v>87.98833819242017</v>
       </c>
       <c r="F4" s="4">
-        <v>78.92737296260719</v>
+        <v>90.05992329817749</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -2308,34 +2671,52 @@
       <c r="M4" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.8018675882794148</v>
+      </c>
+      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.032379213054857</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6686770070154172</v>
+      </c>
+      <c r="R4" s="5">
+        <v>18</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2748920991853083</v>
+        <v>0.3804167156309445</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2509898584915694</v>
+        <v>0.2662192148058027</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2584222619040832</v>
+        <v>0.2583738927069349</v>
       </c>
       <c r="E5" s="4">
-        <v>89.09681729834791</v>
+        <v>89.04458211856162</v>
       </c>
       <c r="F5" s="4">
-        <v>89.57933844678806</v>
+        <v>85.54370405880432</v>
       </c>
       <c r="G5" s="5">
         <v>56</v>
       </c>
       <c r="H5" s="5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I5" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2349,25 +2730,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.1877525352859426</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3970882877210687</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2362323423879764</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.409747959364116</v>
+        <v>0.8720329675280035</v>
       </c>
       <c r="C6" s="4">
-        <v>0.8384029646568754</v>
+        <v>0.4310942811149855</v>
       </c>
       <c r="D6" s="4">
-        <v>1.415867290088196</v>
+        <v>0.8487688410685733</v>
       </c>
       <c r="E6" s="4">
-        <v>87.17687074829945</v>
+        <v>89.18792517006796</v>
       </c>
       <c r="F6" s="4">
-        <v>90.2437546607014</v>
+        <v>91.45274049216955</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
@@ -2390,25 +2789,43 @@
       <c r="M6" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.7167330246252829</v>
+      </c>
+      <c r="O6" s="5">
+        <v>23</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.8198717914455148</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6224879679545035</v>
+      </c>
+      <c r="R6" s="5">
+        <v>20</v>
+      </c>
+      <c r="S6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.391473472980579</v>
+        <v>1.112819628983444</v>
       </c>
       <c r="C7" s="4">
-        <v>1.391473472980579</v>
+        <v>1.112819628983444</v>
       </c>
       <c r="D7" s="4">
-        <v>1.400712192920764</v>
+        <v>1.103062413953686</v>
       </c>
       <c r="E7" s="4">
-        <v>96.87925170068027</v>
+        <v>97.37244897959184</v>
       </c>
       <c r="F7" s="4">
-        <v>97.67337807606263</v>
+        <v>98.00335570469798</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
@@ -2431,25 +2848,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.112819628983444</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.112819628983444</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.5141113835998112</v>
+        <v>0.1850123905568728</v>
       </c>
       <c r="C8" s="4">
-        <v>0.5141113835998112</v>
+        <v>0.1850123905568728</v>
       </c>
       <c r="D8" s="4">
-        <v>0.5571144658752019</v>
+        <v>0.1847726551129016</v>
       </c>
       <c r="E8" s="4">
-        <v>92.24489795918367</v>
+        <v>99.79591836734694</v>
       </c>
       <c r="F8" s="4">
-        <v>95.81096196868008</v>
+        <v>99.22818791946308</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -2472,25 +2905,41 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1850123905568728</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1850123905568728</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.5248960469907615</v>
+        <v>0.1158033590079117</v>
       </c>
       <c r="C9" s="4">
-        <v>0.5248960469907615</v>
+        <v>0.1158033590079117</v>
       </c>
       <c r="D9" s="4">
-        <v>0.5592397664731834</v>
+        <v>0.115815396397444</v>
       </c>
       <c r="E9" s="4">
-        <v>89.25170068027209</v>
+        <v>99.08163265306122</v>
       </c>
       <c r="F9" s="4">
-        <v>91.39821029082773</v>
+        <v>98.55704697986577</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -2513,9 +2962,25 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>2</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1158033590079117</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1158033590079117</v>
+      </c>
+      <c r="R9" s="5">
+        <v>2</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2526,6 +2991,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2533,7 +2999,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2544,9 +3010,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2580,8 +3052,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2603,37 +3083,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.0737111644994</v>
+        <v>0.5176751686562057</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7663227362160493</v>
+        <v>0.3220792214954546</v>
       </c>
       <c r="D3" s="4">
-        <v>1.077334173227428</v>
+        <v>0.51436580609261</v>
       </c>
       <c r="E3" s="4">
-        <v>95.85374149659864</v>
+        <v>93.27721088435374</v>
       </c>
       <c r="F3" s="4">
-        <v>97.39513422818791</v>
+        <v>95.61940715883668</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
       </c>
       <c r="H3" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -2642,39 +3140,57 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3746748738926112</v>
+      </c>
+      <c r="O3" s="5">
+        <v>37</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.602881333006853</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4664011647188764</v>
+      </c>
+      <c r="R3" s="5">
+        <v>34</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.608846502776682</v>
+        <v>1.655174946099578</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9893857694769395</v>
+        <v>0.6351322109252439</v>
       </c>
       <c r="D4" s="4">
-        <v>2.14080167681407</v>
+        <v>1.160493205745297</v>
       </c>
       <c r="E4" s="4">
-        <v>80.22837706511142</v>
+        <v>79.0427599611273</v>
       </c>
       <c r="F4" s="4">
-        <v>80.10626398210348</v>
+        <v>80.22651006711308</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
         <v>13</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2683,42 +3199,60 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.993493705293804</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.257202992600339</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6580755459746936</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4129795167326457</v>
+        <v>0.5288925792379554</v>
       </c>
       <c r="C5" s="4">
-        <v>0.38852175665088</v>
+        <v>0.4838013288986581</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4023657614013376</v>
+        <v>0.5002249870342764</v>
       </c>
       <c r="E5" s="4">
-        <v>93.11163751214769</v>
+        <v>87.66520894071914</v>
       </c>
       <c r="F5" s="4">
-        <v>94.05141418983682</v>
+        <v>83.07086928731083</v>
       </c>
       <c r="G5" s="5">
         <v>56</v>
       </c>
       <c r="H5" s="5">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -2726,37 +3260,55 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.3190837867564874</v>
+      </c>
+      <c r="O5" s="5">
+        <v>36</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5467705539130553</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4279573460997558</v>
+      </c>
+      <c r="R5" s="5">
+        <v>36</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>2.081787468183696</v>
+        <v>1.395430782121972</v>
       </c>
       <c r="C6" s="4">
-        <v>1.117460420999403</v>
+        <v>0.8096344199275336</v>
       </c>
       <c r="D6" s="4">
-        <v>1.976153414635519</v>
+        <v>1.185803948524153</v>
       </c>
       <c r="E6" s="4">
-        <v>85.50453514739226</v>
+        <v>84.12556689342406</v>
       </c>
       <c r="F6" s="4">
-        <v>85.88133855331812</v>
+        <v>84.54651379567515</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I6" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -2765,27 +3317,45 @@
         <v>0</v>
       </c>
       <c r="M6" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-1.369327347664694</v>
+      </c>
+      <c r="O6" s="5">
+        <v>24</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.061498812950958</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.7334279094872856</v>
+      </c>
+      <c r="R6" s="5">
+        <v>21</v>
+      </c>
+      <c r="S6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.745191753772815</v>
+        <v>1.455689133075794</v>
       </c>
       <c r="C7" s="4">
-        <v>1.745191753772815</v>
+        <v>1.455689133075794</v>
       </c>
       <c r="D7" s="4">
-        <v>1.680734814075549</v>
+        <v>1.32079166260155</v>
       </c>
       <c r="E7" s="4">
-        <v>90.76530612244898</v>
+        <v>87.60204081632654</v>
       </c>
       <c r="F7" s="4">
-        <v>91.86241610738254</v>
+        <v>88.8758389261745</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
@@ -2808,25 +3378,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.455689133075794</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.455689133075794</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.8165286618896062</v>
+        <v>0.1570611494098557</v>
       </c>
       <c r="C8" s="4">
-        <v>0.8165286618896062</v>
+        <v>0.1570611494098557</v>
       </c>
       <c r="D8" s="4">
-        <v>0.7999957639403874</v>
+        <v>0.1570649641071213</v>
       </c>
       <c r="E8" s="4">
-        <v>96.93877551020408</v>
+        <v>95.30612244897959</v>
       </c>
       <c r="F8" s="4">
-        <v>95.03355704697987</v>
+        <v>97.4496644295302</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -2849,25 +3435,39 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1570611494098557</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1570611494098557</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>1.05136193978251</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+        <v>0.3062919591611717</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
-        <v>0.9282158826536033</v>
+        <v>0.1225291703885887</v>
       </c>
       <c r="E9" s="4">
-        <v>75.96938775510205</v>
+        <v>61.97278911564625</v>
       </c>
       <c r="F9" s="4">
-        <v>57.57270693512301</v>
+        <v>48.32214765100671</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -2890,9 +3490,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.3062919591611717</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2903,6 +3517,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2910,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2921,9 +3536,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2957,8 +3578,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2980,75 +3609,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.477866123422074</v>
+        <v>1.086917026544688</v>
       </c>
       <c r="C3" s="4">
-        <v>0.477866123422074</v>
+        <v>0.7863394594250066</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4727815581402046</v>
+        <v>1.107068021799205</v>
       </c>
       <c r="E3" s="4">
-        <v>84.46428571428571</v>
+        <v>93.79506802721089</v>
       </c>
       <c r="F3" s="4">
-        <v>91.72846756152127</v>
+        <v>96.05425055928413</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
       </c>
       <c r="H3" s="5">
+        <v>36</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.086917026544688</v>
+      </c>
+      <c r="O3" s="5">
         <v>40</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="P3" s="4">
+        <v>0.7501608000703708</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5651821657290803</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.8930947041434357</v>
+        <v>2.229741956638463</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6806051821331549</v>
+        <v>1.09321489181986</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8589077996106861</v>
+        <v>1.690706159519323</v>
       </c>
       <c r="E4" s="4">
-        <v>78.29203109815323</v>
+        <v>77.48663751214775</v>
       </c>
       <c r="F4" s="4">
-        <v>84.98122403323731</v>
+        <v>78.92737296260719</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -3057,39 +3722,57 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.738234895937889</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.294840871362664</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7128619545388314</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2922316386980798</v>
+        <v>0.2748920991853083</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3052061177677409</v>
+        <v>0.2509898584915694</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3356281522776845</v>
+        <v>0.2584222619040832</v>
       </c>
       <c r="E5" s="4">
-        <v>82.89601554907689</v>
+        <v>89.09681729834791</v>
       </c>
       <c r="F5" s="4">
-        <v>86.71380632789851</v>
+        <v>89.57933844678806</v>
       </c>
       <c r="G5" s="5">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H5" s="5">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I5" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3103,75 +3786,111 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.09536710076350746</v>
+      </c>
+      <c r="O5" s="5">
+        <v>42</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2551970960431038</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2458555180017773</v>
+      </c>
+      <c r="R5" s="5">
+        <v>42</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6786899473327348</v>
+        <v>1.409747959364116</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5853430116124856</v>
+        <v>0.8384029646568754</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6229318447819334</v>
+        <v>1.415867290088196</v>
       </c>
       <c r="E6" s="4">
-        <v>73.67630385487499</v>
+        <v>87.17687074829945</v>
       </c>
       <c r="F6" s="4">
-        <v>80.65902311707563</v>
+        <v>90.2437546607014</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+        <v>4</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-1.39981130314529</v>
+      </c>
+      <c r="O6" s="5">
+        <v>23</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9533570221397051</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6302805447800645</v>
+      </c>
+      <c r="R6" s="5">
+        <v>19</v>
+      </c>
+      <c r="S6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.7825109520235912</v>
+        <v>1.391473472980579</v>
       </c>
       <c r="C7" s="4">
-        <v>0.7310075821442352</v>
+        <v>1.391473472980579</v>
       </c>
       <c r="D7" s="4">
-        <v>0.6773753025809185</v>
+        <v>1.400712192920764</v>
       </c>
       <c r="E7" s="4">
-        <v>66.58163265306122</v>
+        <v>96.87925170068027</v>
       </c>
       <c r="F7" s="4">
-        <v>72.94183445190156</v>
+        <v>97.67337807606263</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -3185,25 +3904,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.391473472980579</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.391473472980579</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.7315158706478611</v>
+        <v>0.5141113835998112</v>
       </c>
       <c r="C8" s="4">
-        <v>0.7315158706478611</v>
+        <v>0.5141113835998112</v>
       </c>
       <c r="D8" s="4">
-        <v>0.7466496091656223</v>
+        <v>0.5571144658752019</v>
       </c>
       <c r="E8" s="4">
-        <v>88.26530612244898</v>
+        <v>92.24489795918367</v>
       </c>
       <c r="F8" s="4">
-        <v>86.67785234899328</v>
+        <v>95.81096196868008</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -3226,34 +3961,50 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.5141113835998112</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.5141113835998112</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3607743467146205</v>
+        <v>0.5248960469907615</v>
       </c>
       <c r="C9" s="4">
-        <v>0</v>
+        <v>0.5248960469907615</v>
       </c>
       <c r="D9" s="4">
-        <v>0.4565044130140519</v>
+        <v>0.5592397664731834</v>
       </c>
       <c r="E9" s="4">
-        <v>53.67346938775511</v>
+        <v>89.25170068027209</v>
       </c>
       <c r="F9" s="4">
-        <v>60.43624161073826</v>
+        <v>91.39821029082773</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -3267,9 +4018,25 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>2</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.5248960469907615</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.5248960469907615</v>
+      </c>
+      <c r="R9" s="5">
+        <v>2</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3280,6 +4047,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3287,7 +4055,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3298,9 +4066,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3334,8 +4108,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3357,25 +4139,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9125199424277485</v>
+        <v>1.0737111644994</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7030506142671378</v>
+        <v>0.7663227362160493</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9087348910223186</v>
+        <v>1.077334173227428</v>
       </c>
       <c r="E3" s="4">
-        <v>93.53316326530613</v>
+        <v>95.85374149659864</v>
       </c>
       <c r="F3" s="4">
-        <v>96.12248322147651</v>
+        <v>97.39513422818791</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
@@ -3384,51 +4184,69 @@
         <v>36</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.0737111644994</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7649093049072689</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5623077160330344</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
         <v>3</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.892493460725467</v>
+        <v>2.608846502776682</v>
       </c>
       <c r="C4" s="4">
-        <v>1.052812774780936</v>
+        <v>0.9893857694769395</v>
       </c>
       <c r="D4" s="4">
-        <v>1.618478992287607</v>
+        <v>2.14080167681407</v>
       </c>
       <c r="E4" s="4">
-        <v>83.15476190476163</v>
+        <v>80.22837706511142</v>
       </c>
       <c r="F4" s="4">
-        <v>83.57382550335637</v>
+        <v>80.10626398210348</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
         <v>13</v>
       </c>
-      <c r="I4" s="5">
-        <v>11</v>
-      </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -3437,36 +4255,54 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>6</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.997625718601921</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.427802909029769</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7807632834693113</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3497140602485054</v>
+        <v>0.4129795167326457</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3182722132431707</v>
+        <v>0.38852175665088</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3480278535862357</v>
+        <v>0.4023657614013376</v>
       </c>
       <c r="E5" s="4">
-        <v>91.42492711370262</v>
+        <v>93.11163751214769</v>
       </c>
       <c r="F5" s="4">
-        <v>92.95022371364625</v>
+        <v>94.05141418983682</v>
       </c>
       <c r="G5" s="5">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H5" s="5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3480,66 +4316,102 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3598577717671287</v>
+      </c>
+      <c r="O5" s="5">
+        <v>50</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2625169154360628</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2573880255728378</v>
+      </c>
+      <c r="R5" s="5">
+        <v>50</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.373499222659704</v>
+        <v>2.081787468183696</v>
       </c>
       <c r="C6" s="4">
-        <v>0.8131517282557525</v>
+        <v>1.117460420999403</v>
       </c>
       <c r="D6" s="4">
-        <v>1.348516274182636</v>
+        <v>1.976153414635519</v>
       </c>
       <c r="E6" s="4">
-        <v>87.67431972789115</v>
+        <v>85.50453514739226</v>
       </c>
       <c r="F6" s="4">
-        <v>90.28337061894068</v>
+        <v>85.88133855331812</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
+        <v>13</v>
+      </c>
+      <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5">
+        <v>6</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>6</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-2.136535589026033</v>
+      </c>
+      <c r="O6" s="5">
         <v>19</v>
       </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="P6" s="4">
+        <v>1.195544874958678</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.8925133558699923</v>
+      </c>
+      <c r="R6" s="5">
+        <v>15</v>
+      </c>
+      <c r="S6" s="5">
         <v>4</v>
       </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.367611397919974</v>
+        <v>1.745191753772815</v>
       </c>
       <c r="C7" s="4">
-        <v>1.367611397919974</v>
+        <v>1.745191753772815</v>
       </c>
       <c r="D7" s="4">
-        <v>1.36142681625279</v>
+        <v>1.680734814075549</v>
       </c>
       <c r="E7" s="4">
-        <v>98.72448979591837</v>
+        <v>90.76530612244898</v>
       </c>
       <c r="F7" s="4">
-        <v>99.24496644295301</v>
+        <v>91.86241610738254</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
@@ -3562,25 +4434,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.745191753772815</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.745191753772815</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.8525466236896744</v>
+        <v>0.8165286618896062</v>
       </c>
       <c r="C8" s="4">
-        <v>0.8525466236896744</v>
+        <v>0.8165286618896062</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8794891524739494</v>
+        <v>0.7999957639403874</v>
       </c>
       <c r="E8" s="4">
-        <v>94.59183673469387</v>
+        <v>96.93877551020408</v>
       </c>
       <c r="F8" s="4">
-        <v>96.74496644295301</v>
+        <v>95.03355704697987</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -3603,34 +4491,48 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.8165286618896062</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.8165286618896062</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.865428416902402</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.865428416902402</v>
-      </c>
+        <v>1.05136193978251</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
-        <v>0.8751599852984935</v>
+        <v>0.9282158826536033</v>
       </c>
       <c r="E9" s="4">
-        <v>91.83673469387755</v>
+        <v>75.96938775510205</v>
       </c>
       <c r="F9" s="4">
-        <v>93.02572706935122</v>
+        <v>57.57270693512301</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -3644,9 +4546,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1.05136193978251</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3657,6 +4573,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3664,7 +4581,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3675,9 +4592,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3711,8 +4634,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3734,25 +4665,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4819726390680549</v>
+        <v>0.477866123422074</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4819726390680549</v>
+        <v>0.477866123422074</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4775401560506095</v>
+        <v>0.4727815581402046</v>
       </c>
       <c r="E3" s="4">
-        <v>84.1079931972789</v>
+        <v>84.46428571428571</v>
       </c>
       <c r="F3" s="4">
-        <v>91.53187919463087</v>
+        <v>91.72846756152127</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
@@ -3775,34 +4724,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02155735472332818</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.472476784741242</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.472476784741242</v>
+      </c>
+      <c r="R3" s="5">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.142524182667086</v>
+        <v>0.8930947041434357</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6160838205099796</v>
+        <v>0.6806051821331549</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8713564790003842</v>
+        <v>0.8589077996106861</v>
       </c>
       <c r="E4" s="4">
-        <v>71.96185617103983</v>
+        <v>78.29203109815323</v>
       </c>
       <c r="F4" s="4">
-        <v>78.57821987855525</v>
+        <v>84.98122403323731</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I4" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -3816,34 +4783,52 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3313583516806951</v>
+      </c>
+      <c r="O4" s="5">
+        <v>20</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8098505646400062</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7320551011053766</v>
+      </c>
+      <c r="R4" s="5">
+        <v>20</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2750414546322406</v>
+        <v>0.2922316386980798</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2949096276434766</v>
+        <v>0.3052061177677409</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3281019833214377</v>
+        <v>0.3356281522776845</v>
       </c>
       <c r="E5" s="4">
-        <v>84.01482021379981</v>
+        <v>82.89601554907689</v>
       </c>
       <c r="F5" s="4">
-        <v>89.13830297219582</v>
+        <v>86.71380632789851</v>
       </c>
       <c r="G5" s="5">
         <v>28</v>
       </c>
       <c r="H5" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3857,75 +4842,111 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.239222452807373</v>
+      </c>
+      <c r="O5" s="5">
+        <v>20</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2693268619443455</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2554383840573439</v>
+      </c>
+      <c r="R5" s="5">
+        <v>20</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6461030863929612</v>
+        <v>0.6786899473327348</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6654468195993321</v>
+        <v>0.5853430116124856</v>
       </c>
       <c r="D6" s="4">
-        <v>0.6348645958511853</v>
+        <v>0.6229318447819334</v>
       </c>
       <c r="E6" s="4">
-        <v>79.91496598639495</v>
+        <v>73.67630385487499</v>
       </c>
       <c r="F6" s="4">
-        <v>87.25904175988222</v>
+        <v>80.65902311707563</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5">
         <v>1</v>
       </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.2010073440918215</v>
+      </c>
+      <c r="O6" s="5">
+        <v>18</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6621141112255112</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5632418968028539</v>
+      </c>
+      <c r="R6" s="5">
+        <v>18</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>0.7295772367397205</v>
+        <v>0.7825109520235912</v>
       </c>
       <c r="C7" s="4">
-        <v>0.7295772367397205</v>
+        <v>0.7310075821442352</v>
       </c>
       <c r="D7" s="4">
-        <v>0.7092200973311321</v>
+        <v>0.6773753025809185</v>
       </c>
       <c r="E7" s="4">
-        <v>86.63265306122449</v>
+        <v>66.58163265306122</v>
       </c>
       <c r="F7" s="4">
-        <v>92.92785234899328</v>
+        <v>72.94183445190156</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -3939,25 +4960,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.7825109520235912</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.7310075821442352</v>
+      </c>
+      <c r="R7" s="5">
+        <v>2</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.7227445554308429</v>
+        <v>0.7315158706478611</v>
       </c>
       <c r="C8" s="4">
-        <v>0.7227445554308429</v>
+        <v>0.7315158706478611</v>
       </c>
       <c r="D8" s="4">
-        <v>0.7393792879156675</v>
+        <v>0.7466496091656223</v>
       </c>
       <c r="E8" s="4">
-        <v>89.08163265306122</v>
+        <v>88.26530612244898</v>
       </c>
       <c r="F8" s="4">
-        <v>86.81208053691275</v>
+        <v>86.67785234899328</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -3980,25 +5017,39 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.7315158706478611</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.7315158706478611</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3495085622125911</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+        <v>0.3607743467146205</v>
+      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
-        <v>0.4439997310692048</v>
+        <v>0.4565044130140519</v>
       </c>
       <c r="E9" s="4">
-        <v>54.48979591836736</v>
+        <v>53.67346938775511</v>
       </c>
       <c r="F9" s="4">
-        <v>60.59284116331097</v>
+        <v>60.43624161073826</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -4021,9 +5072,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.3607743467146205</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4034,6 +5099,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4041,7 +5107,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4052,9 +5118,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4088,8 +5160,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4111,25 +5191,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9941982107411563</v>
+        <v>0.9125199424277485</v>
       </c>
       <c r="C3" s="4">
-        <v>0.711939378850123</v>
+        <v>0.7030506142671378</v>
       </c>
       <c r="D3" s="4">
-        <v>0.9899431811820223</v>
+        <v>0.9087348910223186</v>
       </c>
       <c r="E3" s="4">
-        <v>95.44047619047618</v>
+        <v>93.53316326530613</v>
       </c>
       <c r="F3" s="4">
-        <v>97.17281879194631</v>
+        <v>96.12248322147651</v>
       </c>
       <c r="G3" s="5">
         <v>40</v>
@@ -4138,10 +5236,10 @@
         <v>36</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -4150,36 +5248,54 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.928574294123111</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6853765493853259</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5181676509106524</v>
+      </c>
+      <c r="R3" s="5">
+        <v>36</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.767300042854894</v>
+        <v>1.892493460725467</v>
       </c>
       <c r="C4" s="4">
-        <v>0.9126940228015739</v>
+        <v>1.052812774780936</v>
       </c>
       <c r="D4" s="4">
-        <v>1.564205067630331</v>
+        <v>1.618478992287607</v>
       </c>
       <c r="E4" s="4">
-        <v>84.4776482021376</v>
+        <v>83.15476190476163</v>
       </c>
       <c r="F4" s="4">
-        <v>85.91123362096474</v>
+        <v>83.57382550335637</v>
       </c>
       <c r="G4" s="5">
         <v>28</v>
       </c>
       <c r="H4" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -4193,25 +5309,43 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-1.759193056875047</v>
+      </c>
+      <c r="O4" s="5">
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.095580781017937</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.758755288938356</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2393205445706716</v>
+        <v>0.3497140602485054</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2233330929162867</v>
+        <v>0.3182722132431707</v>
       </c>
       <c r="D5" s="4">
-        <v>0.248267808441592</v>
+        <v>0.3480278535862357</v>
       </c>
       <c r="E5" s="4">
-        <v>92.12099125364431</v>
+        <v>91.42492711370262</v>
       </c>
       <c r="F5" s="4">
-        <v>93.43120805369094</v>
+        <v>92.95022371364625</v>
       </c>
       <c r="G5" s="5">
         <v>28</v>
@@ -4234,34 +5368,52 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2731735028599976</v>
+      </c>
+      <c r="O5" s="5">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2559615250077899</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2423167143081254</v>
+      </c>
+      <c r="R5" s="5">
+        <v>25</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>1.164151990251097</v>
+        <v>1.373499222659704</v>
       </c>
       <c r="C6" s="4">
-        <v>0.6618691171311387</v>
+        <v>0.8131517282557525</v>
       </c>
       <c r="D6" s="4">
-        <v>1.136970775908583</v>
+        <v>1.348516274182636</v>
       </c>
       <c r="E6" s="4">
-        <v>85.1077097505671</v>
+        <v>87.67431972789115</v>
       </c>
       <c r="F6" s="4">
-        <v>86.9630872483238</v>
+        <v>90.28337061894068</v>
       </c>
       <c r="G6" s="5">
         <v>24</v>
       </c>
       <c r="H6" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
         <v>4</v>
@@ -4275,25 +5427,43 @@
       <c r="M6" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-1.362459120850256</v>
+      </c>
+      <c r="O6" s="5">
+        <v>23</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9500835352267866</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6368527338273978</v>
+      </c>
+      <c r="R6" s="5">
+        <v>19</v>
+      </c>
+      <c r="S6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
-        <v>1.295167759923062</v>
+        <v>1.367611397919974</v>
       </c>
       <c r="C7" s="4">
-        <v>1.295167759923062</v>
+        <v>1.367611397919974</v>
       </c>
       <c r="D7" s="4">
-        <v>1.280787349609456</v>
+        <v>1.36142681625279</v>
       </c>
       <c r="E7" s="4">
-        <v>94.76190476190474</v>
+        <v>98.72448979591837</v>
       </c>
       <c r="F7" s="4">
-        <v>95.31599552572708</v>
+        <v>99.24496644295301</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
@@ -4316,25 +5486,41 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.367611397919974</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.367611397919974</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
-        <v>0.8394010055489769</v>
+        <v>0.8525466236896744</v>
       </c>
       <c r="C8" s="4">
-        <v>0.8394010055489769</v>
+        <v>0.8525466236896744</v>
       </c>
       <c r="D8" s="4">
-        <v>0.8174332219786873</v>
+        <v>0.8794891524739494</v>
       </c>
       <c r="E8" s="4">
-        <v>96.22448979591837</v>
+        <v>94.59183673469387</v>
       </c>
       <c r="F8" s="4">
-        <v>95.33557046979865</v>
+        <v>96.74496644295301</v>
       </c>
       <c r="G8" s="5">
         <v>2</v>
@@ -4357,34 +5543,50 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.8525466236896744</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.8525466236896744</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
-        <v>0.9424550448602229</v>
+        <v>0.865428416902402</v>
       </c>
       <c r="C9" s="4">
-        <v>0</v>
+        <v>0.865428416902402</v>
       </c>
       <c r="D9" s="4">
-        <v>0.7210220311826259</v>
+        <v>0.8751599852984935</v>
       </c>
       <c r="E9" s="4">
-        <v>48.87755102040816</v>
+        <v>91.83673469387755</v>
       </c>
       <c r="F9" s="4">
-        <v>49.32885906040269</v>
+        <v>93.02572706935122</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -4398,9 +5600,25 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>2</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.865428416902402</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.865428416902402</v>
+      </c>
+      <c r="R9" s="5">
+        <v>2</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4411,12 +5629,1922 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4819726390680549</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4819726390680549</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4775401560506095</v>
+      </c>
+      <c r="E3" s="4">
+        <v>84.1079931972789</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.53187919463087</v>
+      </c>
+      <c r="G3" s="5">
+        <v>40</v>
+      </c>
+      <c r="H3" s="5">
+        <v>40</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.001329344307297298</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4816403029912305</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4816403029912305</v>
+      </c>
+      <c r="R3" s="5">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.142524182667086</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6160838205099796</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.8713564790003842</v>
+      </c>
+      <c r="E4" s="4">
+        <v>71.96185617103983</v>
+      </c>
+      <c r="F4" s="4">
+        <v>78.57821987855525</v>
+      </c>
+      <c r="G4" s="5">
+        <v>28</v>
+      </c>
+      <c r="H4" s="5">
+        <v>13</v>
+      </c>
+      <c r="I4" s="5">
+        <v>12</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2066585483373972</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.068717558260873</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6951919680483877</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2750414546322406</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2949096276434766</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3281019833214377</v>
+      </c>
+      <c r="E5" s="4">
+        <v>84.01482021379981</v>
+      </c>
+      <c r="F5" s="4">
+        <v>89.13830297219582</v>
+      </c>
+      <c r="G5" s="5">
+        <v>28</v>
+      </c>
+      <c r="H5" s="5">
+        <v>22</v>
+      </c>
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2460647639603535</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2398372154915379</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2536515882646149</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.6461030863929612</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.6654468195993321</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.6348645958511853</v>
+      </c>
+      <c r="E6" s="4">
+        <v>79.91496598639495</v>
+      </c>
+      <c r="F6" s="4">
+        <v>87.25904175988222</v>
+      </c>
+      <c r="G6" s="5">
+        <v>24</v>
+      </c>
+      <c r="H6" s="5">
+        <v>23</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.07607321839610064</v>
+      </c>
+      <c r="O6" s="5">
+        <v>23</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6386025847402269</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6543126779444743</v>
+      </c>
+      <c r="R6" s="5">
+        <v>23</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.7295772367397205</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.7295772367397205</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.7092200973311321</v>
+      </c>
+      <c r="E7" s="4">
+        <v>86.63265306122449</v>
+      </c>
+      <c r="F7" s="4">
+        <v>92.92785234899328</v>
+      </c>
+      <c r="G7" s="5">
+        <v>4</v>
+      </c>
+      <c r="H7" s="5">
+        <v>4</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.7295772367397205</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.7295772367397205</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.7227445554308429</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.7227445554308429</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.7393792879156675</v>
+      </c>
+      <c r="E8" s="4">
+        <v>89.08163265306122</v>
+      </c>
+      <c r="F8" s="4">
+        <v>86.81208053691275</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.7227445554308429</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.7227445554308429</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.3495085622125911</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
+        <v>0.4439997310692048</v>
+      </c>
+      <c r="E9" s="4">
+        <v>54.48979591836736</v>
+      </c>
+      <c r="F9" s="4">
+        <v>60.59284116331097</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.3495085622125911</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9941982107411563</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.711939378850123</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9899431811820223</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.44047619047618</v>
+      </c>
+      <c r="F3" s="4">
+        <v>97.17281879194631</v>
+      </c>
+      <c r="G3" s="5">
+        <v>40</v>
+      </c>
+      <c r="H3" s="5">
+        <v>36</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.9941982107411563</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.720929912180503</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5452396056620286</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.767300042854894</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.9126940228015739</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.564205067630331</v>
+      </c>
+      <c r="E4" s="4">
+        <v>84.4776482021376</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.91123362096474</v>
+      </c>
+      <c r="G4" s="5">
+        <v>28</v>
+      </c>
+      <c r="H4" s="5">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5">
+        <v>9</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-1.583444009756338</v>
+      </c>
+      <c r="O4" s="5">
+        <v>19</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.105188317065542</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7114900949271343</v>
+      </c>
+      <c r="R4" s="5">
+        <v>16</v>
+      </c>
+      <c r="S4" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2393205445706716</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2233330929162867</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.248267808441592</v>
+      </c>
+      <c r="E5" s="4">
+        <v>92.12099125364431</v>
+      </c>
+      <c r="F5" s="4">
+        <v>93.43120805369094</v>
+      </c>
+      <c r="G5" s="5">
+        <v>28</v>
+      </c>
+      <c r="H5" s="5">
+        <v>25</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1055693997716187</v>
+      </c>
+      <c r="O5" s="5">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2239089522122202</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2102948854656859</v>
+      </c>
+      <c r="R5" s="5">
+        <v>25</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1.164151990251097</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.6618691171311387</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.136970775908583</v>
+      </c>
+      <c r="E6" s="4">
+        <v>85.1077097505671</v>
+      </c>
+      <c r="F6" s="4">
+        <v>86.9630872483238</v>
+      </c>
+      <c r="G6" s="5">
+        <v>24</v>
+      </c>
+      <c r="H6" s="5">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>4</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-1.210418963544619</v>
+      </c>
+      <c r="O6" s="5">
+        <v>21</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9613098431468359</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6502418405148385</v>
+      </c>
+      <c r="R6" s="5">
+        <v>17</v>
+      </c>
+      <c r="S6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.295167759923062</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.295167759923062</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.280787349609456</v>
+      </c>
+      <c r="E7" s="4">
+        <v>94.76190476190474</v>
+      </c>
+      <c r="F7" s="4">
+        <v>95.31599552572708</v>
+      </c>
+      <c r="G7" s="5">
+        <v>4</v>
+      </c>
+      <c r="H7" s="5">
+        <v>4</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.295167759923062</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.295167759923062</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.8394010055489769</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.8394010055489769</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.8174332219786873</v>
+      </c>
+      <c r="E8" s="4">
+        <v>96.22448979591837</v>
+      </c>
+      <c r="F8" s="4">
+        <v>95.33557046979865</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.8394010055489769</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.8394010055489769</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.9424550448602229</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4">
+        <v>0.7210220311826259</v>
+      </c>
+      <c r="E9" s="4">
+        <v>48.87755102040816</v>
+      </c>
+      <c r="F9" s="4">
+        <v>49.32885906040269</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.9424550448602229</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>78.2051282051282</v>
+      </c>
+      <c r="C3" s="3">
+        <v>13.46153846153846</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.8790829826918648</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5219263786665772</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.8422255053172096</v>
+      </c>
+      <c r="K3" s="4">
+        <v>88.99071166928289</v>
+      </c>
+      <c r="L3" s="4">
+        <v>90.14455343314377</v>
+      </c>
+      <c r="M3" s="5">
+        <v>156</v>
+      </c>
+      <c r="N3" s="5">
+        <v>359090.4123783112</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.50569497404826</v>
+      </c>
+      <c r="P3" s="5">
+        <v>11047</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C4" s="3">
+        <v>24.35897435897436</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.962435634802683</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.5110586264145832</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.9137926266475802</v>
+      </c>
+      <c r="K4" s="4">
+        <v>81.82779522065235</v>
+      </c>
+      <c r="L4" s="4">
+        <v>83.65004588997927</v>
+      </c>
+      <c r="M4" s="5">
+        <v>156</v>
+      </c>
+      <c r="N4" s="5">
+        <v>810659.9159240723</v>
+      </c>
+      <c r="O4" s="4">
+        <v>45.6093122495821</v>
+      </c>
+      <c r="P4" s="5">
+        <v>17774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>66.02564102564102</v>
+      </c>
+      <c r="C5" s="3">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.205128205128205</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.8180474654000987</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.5731154904668406</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.7345134391013389</v>
+      </c>
+      <c r="K5" s="4">
+        <v>87.41910866910877</v>
+      </c>
+      <c r="L5" s="4">
+        <v>86.87646991338381</v>
+      </c>
+      <c r="M5" s="5">
+        <v>156</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2296413.82598877</v>
+      </c>
+      <c r="O5" s="4">
+        <v>143.1054917423051</v>
+      </c>
+      <c r="P5" s="5">
+        <v>16047</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>68.58974358974359</v>
+      </c>
+      <c r="C6" s="3">
+        <v>23.71794871794872</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.8119164069414717</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.5324822294927277</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.7224479058674282</v>
+      </c>
+      <c r="K6" s="4">
+        <v>86.04330193615884</v>
+      </c>
+      <c r="L6" s="4">
+        <v>86.17757987724386</v>
+      </c>
+      <c r="M6" s="5">
+        <v>156</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1481218.880176544</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.22237335398556</v>
+      </c>
+      <c r="P6" s="5">
+        <v>17587</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>53.2051282051282</v>
+      </c>
+      <c r="C7" s="3">
+        <v>17.30769230769231</v>
+      </c>
+      <c r="D7" s="3">
+        <v>29.48717948717949</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>29.48717948717949</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.573615709228179</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.4883602039838482</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1.507181508138613</v>
+      </c>
+      <c r="K7" s="4">
+        <v>89.93764172335555</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.83326163024226</v>
+      </c>
+      <c r="M7" s="5">
+        <v>156</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1644880.89799881</v>
+      </c>
+      <c r="O7" s="4">
+        <v>172.2208038947555</v>
+      </c>
+      <c r="P7" s="5">
+        <v>9551</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3">
+        <v>16.02564102564103</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.974358974358974</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.641025641025641</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.071086610348392</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.7596910088866733</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1.027021922984266</v>
+      </c>
+      <c r="K8" s="4">
+        <v>88.23805163090869</v>
+      </c>
+      <c r="L8" s="4">
+        <v>88.6215797625179</v>
+      </c>
+      <c r="M8" s="5">
+        <v>156</v>
+      </c>
+      <c r="N8" s="5">
+        <v>211118.9484596252</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.78269244730112</v>
+      </c>
+      <c r="P8" s="5">
+        <v>16516</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>72.43589743589743</v>
+      </c>
+      <c r="C9" s="3">
+        <v>20.51282051282051</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7.051282051282051</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.641025641025641</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.9756149704347047</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.5210440562759608</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.9126978373090483</v>
+      </c>
+      <c r="K9" s="4">
+        <v>85.76399790685457</v>
+      </c>
+      <c r="L9" s="4">
+        <v>86.78002925486018</v>
+      </c>
+      <c r="M9" s="5">
+        <v>156</v>
+      </c>
+      <c r="N9" s="5">
+        <v>550822.2744464874</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.85810247433258</v>
+      </c>
+      <c r="P9" s="5">
+        <v>18448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>82.69230769230769</v>
+      </c>
+      <c r="C10" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="D10" s="3">
+        <v>4.487179487179487</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4.487179487179487</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.6279315781267164</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.4647664972647436</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.5536020073615655</v>
+      </c>
+      <c r="K10" s="4">
+        <v>91.11111111111083</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.99387655595902</v>
+      </c>
+      <c r="M10" s="5">
+        <v>156</v>
+      </c>
+      <c r="N10" s="5">
+        <v>981849.686384201</v>
+      </c>
+      <c r="O10" s="4">
+        <v>101.2320534471802</v>
+      </c>
+      <c r="P10" s="5">
+        <v>9699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>70.51282051282051</v>
+      </c>
+      <c r="C11" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6.41025641025641</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.282051282051282</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.7830866820030957</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.5577995553459991</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.6789002386461876</v>
+      </c>
+      <c r="K11" s="4">
+        <v>86.77895517181216</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.89263179028309</v>
+      </c>
+      <c r="M11" s="5">
+        <v>156</v>
+      </c>
+      <c r="N11" s="5">
+        <v>622117.4757480621</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.93820862477127</v>
+      </c>
+      <c r="P11" s="5">
+        <v>15577</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>75.64102564102564</v>
+      </c>
+      <c r="C12" s="3">
+        <v>18.58974358974359</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.7120351991271772</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.5034852071732312</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.6691275931969591</v>
+      </c>
+      <c r="K12" s="4">
+        <v>88.16413744985213</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.74064991682324</v>
+      </c>
+      <c r="M12" s="5">
+        <v>156</v>
+      </c>
+      <c r="N12" s="5">
+        <v>258279.8476219177</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.08941963207078</v>
+      </c>
+      <c r="P12" s="5">
+        <v>13530</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>77.56410256410257</v>
+      </c>
+      <c r="C13" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.7992655521217151</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.5440184639164097</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.7540911187459863</v>
+      </c>
+      <c r="K13" s="4">
+        <v>90.10116867259715</v>
+      </c>
+      <c r="L13" s="4">
+        <v>90.63765559571105</v>
+      </c>
+      <c r="M13" s="5">
+        <v>156</v>
+      </c>
+      <c r="N13" s="5">
+        <v>768031.3620567322</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.14256348500726</v>
+      </c>
+      <c r="P13" s="5">
+        <v>9956</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>79.6875</v>
+      </c>
+      <c r="C14" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.5493859550487743</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.5069837464798006</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5351729356805436</v>
+      </c>
+      <c r="K14" s="4">
+        <v>79.76775085034011</v>
+      </c>
+      <c r="L14" s="4">
+        <v>85.92509088366927</v>
+      </c>
+      <c r="M14" s="5">
+        <v>128</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2749436.969041824</v>
+      </c>
+      <c r="O14" s="4">
+        <v>235.6189021374432</v>
+      </c>
+      <c r="P14" s="5">
+        <v>11669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>79.6875</v>
+      </c>
+      <c r="C15" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7.8125</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>7.8125</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.757551930175315</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.5523639701098846</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.7602691727515468</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.85544217687074</v>
+      </c>
+      <c r="L15" s="4">
+        <v>91.64761605145415</v>
+      </c>
+      <c r="M15" s="5">
+        <v>128</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2227689.119577408</v>
+      </c>
+      <c r="O15" s="4">
+        <v>242.4036038713175</v>
+      </c>
+      <c r="P15" s="5">
+        <v>9190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>82.03125</v>
+      </c>
+      <c r="C16" s="3">
+        <v>16.40625</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.5625</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.78125</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.78125</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5960501796931869</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.5142059453780158</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.5483261588477241</v>
+      </c>
+      <c r="K16" s="4">
+        <v>80.33827593537414</v>
+      </c>
+      <c r="L16" s="4">
+        <v>86.85996923937351</v>
+      </c>
+      <c r="M16" s="5">
+        <v>128</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1103922.834396362</v>
+      </c>
+      <c r="O16" s="4">
+        <v>94.00688362397703</v>
+      </c>
+      <c r="P16" s="5">
+        <v>11743</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>78.90625</v>
+      </c>
+      <c r="C17" s="3">
+        <v>13.28125</v>
+      </c>
+      <c r="D17" s="3">
+        <v>7.8125</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>7.8125</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.7645917140861889</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.5418679545001367</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.7525714081428601</v>
+      </c>
+      <c r="K17" s="4">
+        <v>89.64232568027199</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.14225041946256</v>
+      </c>
+      <c r="M17" s="5">
+        <v>128</v>
+      </c>
+      <c r="N17" s="5">
+        <v>943117.1712875366</v>
+      </c>
+      <c r="O17" s="4">
+        <v>105.3644476916028</v>
+      </c>
+      <c r="P17" s="5">
+        <v>8951</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4750,7 +7878,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -5171,9 +8299,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>122</v>
+      </c>
+      <c r="C3" s="5">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>108</v>
+      </c>
+      <c r="C4" s="5">
+        <v>38</v>
+      </c>
+      <c r="D4" s="5">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>103</v>
+      </c>
+      <c r="C5" s="5">
+        <v>39</v>
+      </c>
+      <c r="D5" s="5">
+        <v>14</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>107</v>
+      </c>
+      <c r="C6" s="5">
+        <v>37</v>
+      </c>
+      <c r="D6" s="5">
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>9</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>83</v>
+      </c>
+      <c r="C7" s="5">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5">
+        <v>46</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>46</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>117</v>
+      </c>
+      <c r="C8" s="5">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5">
+        <v>14</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>113</v>
+      </c>
+      <c r="C9" s="5">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>129</v>
+      </c>
+      <c r="C10" s="5">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5">
+        <v>7</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>7</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>110</v>
+      </c>
+      <c r="C11" s="5">
+        <v>36</v>
+      </c>
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>8</v>
+      </c>
+      <c r="H11" s="5">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>118</v>
+      </c>
+      <c r="C12" s="5">
+        <v>29</v>
+      </c>
+      <c r="D12" s="5">
+        <v>9</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>9</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>121</v>
+      </c>
+      <c r="C13" s="5">
+        <v>26</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>9</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>102</v>
+      </c>
+      <c r="C14" s="5">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>102</v>
+      </c>
+      <c r="C15" s="5">
+        <v>16</v>
+      </c>
+      <c r="D15" s="5">
+        <v>10</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>105</v>
+      </c>
+      <c r="C16" s="5">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>101</v>
+      </c>
+      <c r="C17" s="5">
+        <v>17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>10</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>10</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5184,9 +9067,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5220,8 +9109,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5243,10 +9140,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.401307065988658</v>
@@ -5284,10 +9199,28 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.401307065988658</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8521802323364682</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6182657061123471</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>3.071717304974819</v>
@@ -5325,10 +9258,28 @@
       <c r="M4" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-2.597122091525047</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.524524287593002</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8319610152332079</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3376340941922535</v>
@@ -5366,10 +9317,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2845348969211854</v>
+      </c>
+      <c r="O5" s="5">
+        <v>54</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2439679496817426</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2379182856988666</v>
+      </c>
+      <c r="R5" s="5">
+        <v>54</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>2.954099894750774</v>
@@ -5407,17 +9376,33 @@
       <c r="M6" s="5">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-2.99728656241946</v>
+      </c>
+      <c r="O6" s="5">
+        <v>21</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.43122808273959</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.972272373045565</v>
+      </c>
+      <c r="R6" s="5">
+        <v>17</v>
+      </c>
+      <c r="S6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>2.153937757877429</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4">
         <v>2.105599344638904</v>
       </c>
@@ -5448,10 +9433,24 @@
       <c r="M7" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2.153937757877429</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>0.7197185594268376</v>
@@ -5489,17 +9488,31 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.7197185594268376</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.7197185594268376</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
         <v>1.148094317788491</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
         <v>1.018181464547524</v>
       </c>
@@ -5530,9 +9543,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1.148094317788491</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5543,14 +9570,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5561,9 +9589,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5597,8 +9631,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5620,10 +9662,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.497472818399547</v>
@@ -5661,10 +9721,28 @@
       <c r="M3" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.483376115875561</v>
+      </c>
+      <c r="O3" s="5">
+        <v>37</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9113886362963182</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6578638558637135</v>
+      </c>
+      <c r="R3" s="5">
+        <v>34</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>3.398828285213053</v>
@@ -5702,10 +9780,28 @@
       <c r="M4" s="5">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-2.911728979478669</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.617571489226455</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8878847694938617</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2969397534364231</v>
@@ -5743,10 +9839,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2152230490005009</v>
+      </c>
+      <c r="O5" s="5">
+        <v>44</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2534657981742538</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2307650599240716</v>
+      </c>
+      <c r="R5" s="5">
+        <v>44</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>3.709460398742218</v>
@@ -5784,17 +9898,33 @@
       <c r="M6" s="5">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-3.470290800249801</v>
+      </c>
+      <c r="O6" s="5">
+        <v>19</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.58531873852928</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.6108088284333318</v>
+      </c>
+      <c r="R6" s="5">
+        <v>16</v>
+      </c>
+      <c r="S6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>2.538540542987903</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
+      <c r="C7" s="4"/>
       <c r="D7" s="4">
         <v>2.428399861721118</v>
       </c>
@@ -5825,10 +9955,24 @@
       <c r="M7" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2.538540542987903</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>1.122869713944965</v>
@@ -5866,17 +10010,31 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1.122869713944965</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>1.122869713944965</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
         <v>1.875387928361306</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
         <v>1.332251927728066</v>
       </c>
@@ -5907,9 +10065,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1.875387928361306</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5920,14 +10092,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5938,9 +10111,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5974,8 +10153,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5997,10 +10184,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.8890735772372864</v>
@@ -6038,10 +10243,28 @@
       <c r="M3" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.9084255821393239</v>
+      </c>
+      <c r="O3" s="5">
+        <v>38</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7168079096587845</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5405945507806673</v>
+      </c>
+      <c r="R3" s="5">
+        <v>35</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>2.428876317105148</v>
@@ -6079,10 +10302,28 @@
       <c r="M4" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-1.986312426883939</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.319827427960782</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7401518059744245</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6434897823078894</v>
@@ -6120,10 +10361,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3929330804574803</v>
+      </c>
+      <c r="O5" s="5">
+        <v>38</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4460148744342713</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2945937045630452</v>
+      </c>
+      <c r="R5" s="5">
+        <v>38</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.781843412606577</v>
@@ -6161,10 +10420,28 @@
       <c r="M6" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-1.866638202207014</v>
+      </c>
+      <c r="O6" s="5">
+        <v>16</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.158559396743802</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.034125697318359</v>
+      </c>
+      <c r="R6" s="5">
+        <v>12</v>
+      </c>
+      <c r="S6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>1.616849929956516</v>
@@ -6202,10 +10479,26 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.616849929956516</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.616849929956516</v>
+      </c>
+      <c r="R7" s="5">
+        <v>4</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>0.5783978540130192</v>
@@ -6243,17 +10536,31 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.5783978540130192</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.5783978540130192</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
         <v>0.7907331575697754</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
         <v>0.5763087187951896</v>
       </c>
@@ -6284,9 +10591,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.7907331575697754</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6297,14 +10618,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6315,9 +10637,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -6351,8 +10679,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6374,10 +10710,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.8473733113081835</v>
@@ -6415,10 +10769,28 @@
       <c r="M3" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.8397553997288923</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7017592804932065</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5256522590776662</v>
+      </c>
+      <c r="R3" s="5">
+        <v>37</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>2.138652094904891</v>
@@ -6456,10 +10828,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-1.706633971399181</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.254133070280208</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6515910635160533</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.495047819093088</v>
@@ -6497,10 +10887,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2000862948302827</v>
+      </c>
+      <c r="O5" s="5">
+        <v>39</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4101215667861376</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2413326879744531</v>
+      </c>
+      <c r="R5" s="5">
+        <v>39</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>2.152252158710022</v>
@@ -6538,10 +10946,28 @@
       <c r="M6" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-2.311282611897588</v>
+      </c>
+      <c r="O6" s="5">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.271585996812759</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>1.025789637393418</v>
+      </c>
+      <c r="R6" s="5">
+        <v>13</v>
+      </c>
+      <c r="S6" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>1.797177017597278</v>
@@ -6579,10 +11005,26 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>3</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.797177017597278</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.798200925067552</v>
+      </c>
+      <c r="R7" s="5">
+        <v>3</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>0.4569691259093815</v>
@@ -6620,17 +11062,31 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.4569691259093815</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.4569691259093815</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
         <v>0.9426721547788475</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
+      <c r="C9" s="4"/>
       <c r="D9" s="4">
         <v>0.793545625085244</v>
       </c>
@@ -6661,9 +11117,23 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.9426721547788475</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -6674,14 +11144,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -6692,9 +11163,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -6728,8 +11205,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6751,10 +11236,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.4881555667514476</v>
@@ -6792,10 +11295,28 @@
       <c r="M3" s="5">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3191753940831404</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5629153918044902</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4701993036948567</v>
+      </c>
+      <c r="R3" s="5">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.643635406042449</v>
@@ -6833,10 +11354,28 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-1.010799274678448</v>
+      </c>
+      <c r="O4" s="5">
+        <v>16</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.262441090018521</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6856646566339545</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.980050389024524</v>
@@ -6874,10 +11413,28 @@
       <c r="M5" s="5">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>2.908831908808073</v>
+      </c>
+      <c r="O5" s="5">
+        <v>48</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.88686260616791</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1482415821984281</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.008905259357258</v>
@@ -6915,10 +11472,28 @@
       <c r="M6" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.6212069327064254</v>
+      </c>
+      <c r="O6" s="5">
+        <v>18</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.8629986843870938</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.4925315458600987</v>
+      </c>
+      <c r="R6" s="5">
+        <v>16</v>
+      </c>
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B7" s="4">
         <v>1.174265802768787</v>
@@ -6956,10 +11531,26 @@
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4"/>
+      <c r="O7" s="5">
+        <v>3</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1.174265802768787</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1.151611313633718</v>
+      </c>
+      <c r="R7" s="5">
+        <v>3</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="4">
         <v>0.1570649641071213</v>
@@ -6997,10 +11588,26 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4"/>
+      <c r="O8" s="5">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1570649641071213</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1570649641071213</v>
+      </c>
+      <c r="R8" s="5">
+        <v>2</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B9" s="4">
         <v>0.1158084684575442</v>
@@ -7038,9 +11645,25 @@
       <c r="M9" s="5">
         <v>0</v>
       </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5">
+        <v>2</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1158084684575442</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1158084684575442</v>
+      </c>
+      <c r="R9" s="5">
+        <v>2</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -7051,760 +11674,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.149870972698643</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8246028319952297</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.136932554722177</v>
-      </c>
-      <c r="E3" s="4">
-        <v>94.67602040816327</v>
-      </c>
-      <c r="F3" s="4">
-        <v>96.57298657718121</v>
-      </c>
-      <c r="G3" s="5">
-        <v>40</v>
-      </c>
-      <c r="H3" s="5">
-        <v>36</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2.670330691312031</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.085743198894969</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2.125306840314905</v>
-      </c>
-      <c r="E4" s="4">
-        <v>77.9421768707479</v>
-      </c>
-      <c r="F4" s="4">
-        <v>79.65484180249257</v>
-      </c>
-      <c r="G4" s="5">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5">
-        <v>8</v>
-      </c>
-      <c r="I4" s="5">
-        <v>12</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.28125693655206</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4727303005313027</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.208653347729461</v>
-      </c>
-      <c r="E5" s="4">
-        <v>90.54664723032076</v>
-      </c>
-      <c r="F5" s="4">
-        <v>89.14789069990286</v>
-      </c>
-      <c r="G5" s="5">
-        <v>56</v>
-      </c>
-      <c r="H5" s="5">
-        <v>32</v>
-      </c>
-      <c r="I5" s="5">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.931029961421386</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.090191500168673</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1.849495096907873</v>
-      </c>
-      <c r="E6" s="4">
-        <v>85.45918367346938</v>
-      </c>
-      <c r="F6" s="4">
-        <v>86.41918344518992</v>
-      </c>
-      <c r="G6" s="5">
-        <v>24</v>
-      </c>
-      <c r="H6" s="5">
-        <v>16</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>7</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1.687427134780928</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.687427134780928</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1.653930127278302</v>
-      </c>
-      <c r="E7" s="4">
-        <v>93.16326530612245</v>
-      </c>
-      <c r="F7" s="4">
-        <v>93.35570469798658</v>
-      </c>
-      <c r="G7" s="5">
-        <v>4</v>
-      </c>
-      <c r="H7" s="5">
-        <v>4</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.3631239746225166</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.3631239746225166</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.3645609420697369</v>
-      </c>
-      <c r="E8" s="4">
-        <v>95.40816326530613</v>
-      </c>
-      <c r="F8" s="4">
-        <v>97.08053691275168</v>
-      </c>
-      <c r="G8" s="5">
-        <v>2</v>
-      </c>
-      <c r="H8" s="5">
-        <v>2</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0.7530025178834512</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.5236403675151209</v>
-      </c>
-      <c r="E9" s="4">
-        <v>55.30612244897959</v>
-      </c>
-      <c r="F9" s="4">
-        <v>48.89261744966443</v>
-      </c>
-      <c r="G9" s="5">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>2</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.388262136484264</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.036059950682517</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.372024972940562</v>
-      </c>
-      <c r="E3" s="4">
-        <v>94.13095238095238</v>
-      </c>
-      <c r="F3" s="4">
-        <v>96.05816554809844</v>
-      </c>
-      <c r="G3" s="5">
-        <v>40</v>
-      </c>
-      <c r="H3" s="5">
-        <v>35</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>3.520654039855539</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.42583879918493</v>
-      </c>
-      <c r="D4" s="4">
-        <v>3.068898584293493</v>
-      </c>
-      <c r="E4" s="4">
-        <v>80.50170068027208</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.31743368488327</v>
-      </c>
-      <c r="G4" s="5">
-        <v>28</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5">
-        <v>14</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3345885537234738</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3065869533369551</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3226438545160428</v>
-      </c>
-      <c r="E5" s="4">
-        <v>90.89042759961124</v>
-      </c>
-      <c r="F5" s="4">
-        <v>90.91343080856491</v>
-      </c>
-      <c r="G5" s="5">
-        <v>56</v>
-      </c>
-      <c r="H5" s="5">
-        <v>50</v>
-      </c>
-      <c r="I5" s="5">
-        <v>6</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>3.400544724055786</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.533573480327808</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3.019866348493755</v>
-      </c>
-      <c r="E6" s="4">
-        <v>71.6439909297053</v>
-      </c>
-      <c r="F6" s="4">
-        <v>73.19258016405635</v>
-      </c>
-      <c r="G6" s="5">
-        <v>24</v>
-      </c>
-      <c r="H6" s="5">
-        <v>3</v>
-      </c>
-      <c r="I6" s="5">
-        <v>9</v>
-      </c>
-      <c r="J6" s="5">
-        <v>12</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2.422941625980457</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2.158248127369006</v>
-      </c>
-      <c r="E7" s="4">
-        <v>67.14285714285714</v>
-      </c>
-      <c r="F7" s="4">
-        <v>68.93456375838926</v>
-      </c>
-      <c r="G7" s="5">
-        <v>4</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>2</v>
-      </c>
-      <c r="J7" s="5">
-        <v>2</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.423597915811115</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1.170272215051227</v>
-      </c>
-      <c r="E8" s="4">
-        <v>85.10204081632654</v>
-      </c>
-      <c r="F8" s="4">
-        <v>79.83221476510067</v>
-      </c>
-      <c r="G8" s="5">
-        <v>2</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5">
-        <v>2</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1.928359172219643</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1.079299828881631</v>
-      </c>
-      <c r="E9" s="4">
-        <v>55.90136054421769</v>
-      </c>
-      <c r="F9" s="4">
-        <v>53.64653243847874</v>
-      </c>
-      <c r="G9" s="5">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>2</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/FantaQMCcopperCO2024.xlsx
+++ b/public/downloads/FantaQMCcopperCO2024.xlsx
@@ -1569,22 +1569,22 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.149870972698643</v>
+        <v>-0.6329546455914539</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7871002672722581</v>
+        <v>0.7240080982057522</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5779316120488628</v>
+        <v>0.4217501542910675</v>
       </c>
       <c r="R3" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -1628,16 +1628,16 @@
         <v>7</v>
       </c>
       <c r="N4" s="4">
-        <v>-2.172882659272688</v>
+        <v>-1.727439041027233</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>1.419460870467524</v>
+        <v>1.47634037302195</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7095762312878977</v>
+        <v>0.6053883585785391</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -1687,16 +1687,16 @@
         <v>14</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.13729352910163</v>
+        <v>-0.6724017514886924</v>
       </c>
       <c r="O5" s="5">
         <v>46</v>
       </c>
       <c r="P5" s="4">
-        <v>1.060600583422991</v>
+        <v>1.031500006942262</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.8753370723954619</v>
+        <v>0.7782745124198853</v>
       </c>
       <c r="R5" s="5">
         <v>42</v>
@@ -1746,16 +1746,16 @@
         <v>7</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.939510650697573</v>
+        <v>-1.312415294261472</v>
       </c>
       <c r="O6" s="5">
         <v>23</v>
       </c>
       <c r="P6" s="4">
-        <v>1.145208414772707</v>
+        <v>1.085973734096552</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.7387249399058962</v>
+        <v>0.5203019907926729</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -2095,16 +2095,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.40096893360598</v>
+        <v>-0.9244789623771794</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8597941328300432</v>
+        <v>0.7937637992839882</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6254460085616417</v>
+        <v>0.5256073062199802</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -2154,22 +2154,22 @@
         <v>13</v>
       </c>
       <c r="N4" s="4">
-        <v>-3.060926337398996</v>
+        <v>-2.255937013265793</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>1.660313642044847</v>
+        <v>1.646518573916962</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7594021782533673</v>
+        <v>0.61658410239761</v>
       </c>
       <c r="R4" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -2213,16 +2213,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1789593724141014</v>
+        <v>-0.07483911482268013</v>
       </c>
       <c r="O5" s="5">
         <v>50</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3155410502200539</v>
+        <v>0.3170626139219946</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3029212732286542</v>
+        <v>0.29593859453802</v>
       </c>
       <c r="R5" s="5">
         <v>50</v>
@@ -2272,16 +2272,16 @@
         <v>12</v>
       </c>
       <c r="N6" s="4">
-        <v>-3.258119334041839</v>
+        <v>-2.681316691232496</v>
       </c>
       <c r="O6" s="5">
         <v>15</v>
       </c>
       <c r="P6" s="4">
-        <v>1.552058691877088</v>
+        <v>1.461482303120344</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.8141713764603572</v>
+        <v>0.638428869620279</v>
       </c>
       <c r="R6" s="5">
         <v>13</v>
@@ -2613,22 +2613,22 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.225104773083747</v>
+        <v>0.04868240030293158</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5520982775024054</v>
+        <v>0.5030452852401309</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.513379476452565</v>
+        <v>0.362317814134263</v>
       </c>
       <c r="R3" s="5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -2672,16 +2672,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8018675882794148</v>
+        <v>-0.8204488020489151</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>1.032379213054857</v>
+        <v>1.029724753944929</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6686770070154172</v>
+        <v>0.6707415863231394</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -2731,16 +2731,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1877525352859426</v>
+        <v>0.1350124248429991</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3970882877210687</v>
+        <v>0.3841579919124349</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2362323423879764</v>
+        <v>0.2341592687523362</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -2790,22 +2790,22 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.7167330246252829</v>
+        <v>-0.2255624951375381</v>
       </c>
       <c r="O6" s="5">
         <v>23</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8198717914455148</v>
+        <v>0.79757041305893</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6224879679545035</v>
+        <v>0.3963948689270866</v>
       </c>
       <c r="R6" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -3143,16 +3143,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3746748738926112</v>
+        <v>0.0207609022181714</v>
       </c>
       <c r="O3" s="5">
         <v>37</v>
       </c>
       <c r="P3" s="4">
-        <v>0.602881333006853</v>
+        <v>0.5166489662486129</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4664011647188764</v>
+        <v>0.3184294654608547</v>
       </c>
       <c r="R3" s="5">
         <v>34</v>
@@ -3202,16 +3202,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.993493705293804</v>
+        <v>-1.153300905469223</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>1.257202992600339</v>
+        <v>1.209727897707385</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6580755459746936</v>
+        <v>0.6703684075266489</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -3261,16 +3261,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3190837867564874</v>
+        <v>0.2984481441417302</v>
       </c>
       <c r="O5" s="5">
         <v>36</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5467705539130553</v>
+        <v>0.5413939715807439</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4279573460997558</v>
+        <v>0.426898379787316</v>
       </c>
       <c r="R5" s="5">
         <v>36</v>
@@ -3320,22 +3320,22 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.369327347664694</v>
+        <v>-0.8658904960175278</v>
       </c>
       <c r="O6" s="5">
         <v>24</v>
       </c>
       <c r="P6" s="4">
-        <v>1.061498812950958</v>
+        <v>0.9821959101939987</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.7334279094872856</v>
+        <v>0.4869306728174706</v>
       </c>
       <c r="R6" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -3669,22 +3669,22 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.086917026544688</v>
+        <v>-0.5968475704248704</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7501608000703708</v>
+        <v>0.6944005845496577</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5651821657290803</v>
+        <v>0.4165264761444026</v>
       </c>
       <c r="R3" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -3728,16 +3728,16 @@
         <v>3</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.738234895937889</v>
+        <v>-1.440952992634266</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>1.294840871362664</v>
+        <v>1.343376782168759</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7128619545388314</v>
+        <v>0.6154606147410959</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -3787,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.09536710076350746</v>
+        <v>-0.07954707884346135</v>
       </c>
       <c r="O5" s="5">
         <v>42</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2551970960431038</v>
+        <v>0.2569227346370359</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2458555180017773</v>
+        <v>0.2451430319517732</v>
       </c>
       <c r="R5" s="5">
         <v>42</v>
@@ -3846,16 +3846,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.39981130314529</v>
+        <v>-0.8665480105555616</v>
       </c>
       <c r="O6" s="5">
         <v>23</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9533570221397051</v>
+        <v>0.9335196814345181</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6302805447800645</v>
+        <v>0.4648904058393734</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -4199,16 +4199,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.0737111644994</v>
+        <v>-0.5352126406869502</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7649093049072689</v>
+        <v>0.6985364316413325</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5623077160330344</v>
+        <v>0.4468912159769585</v>
       </c>
       <c r="R3" s="5">
         <v>37</v>
@@ -4258,16 +4258,16 @@
         <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.997625718601921</v>
+        <v>-1.642117625051469</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>1.427802909029769</v>
+        <v>1.488105809071775</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7807632834693113</v>
+        <v>0.6477675389167137</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -4317,16 +4317,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3598577717671287</v>
+        <v>-0.3112306260263722</v>
       </c>
       <c r="O5" s="5">
         <v>50</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2625169154360628</v>
+        <v>0.2631479216856211</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2573880255728378</v>
+        <v>0.2561496667427127</v>
       </c>
       <c r="R5" s="5">
         <v>50</v>
@@ -4376,16 +4376,16 @@
         <v>6</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.136535589026033</v>
+        <v>-1.373282687171013</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>1.195544874958678</v>
+        <v>1.127516473579514</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.8925133558699923</v>
+        <v>0.4595419675873321</v>
       </c>
       <c r="R6" s="5">
         <v>15</v>
@@ -4725,16 +4725,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02155735472332818</v>
+        <v>0.237072950156282</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.472476784741242</v>
+        <v>0.4275883883809106</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.472476784741242</v>
+        <v>0.4275883883809106</v>
       </c>
       <c r="R3" s="5">
         <v>40</v>
@@ -4784,16 +4784,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3313583516806951</v>
+        <v>-0.3761370430074646</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8098505646400062</v>
+        <v>0.8085577893621966</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7320551011053766</v>
+        <v>0.7302452157164432</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -4843,16 +4843,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.239222452807373</v>
+        <v>0.2146693415561458</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2693268619443455</v>
+        <v>0.2645575180774488</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2554383840573439</v>
+        <v>0.2536719248939341</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -4902,13 +4902,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2010073440918215</v>
+        <v>0.1929419304469788</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>0.6621141112255112</v>
+        <v>0.6621141112255111</v>
       </c>
       <c r="Q6" s="4">
         <v>0.5632418968028539</v>
@@ -5251,16 +5251,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.928574294123111</v>
+        <v>-0.5208602051861817</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6853765493853259</v>
+        <v>0.6237580588469376</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5181676509106524</v>
+        <v>0.4270518787048362</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -5310,16 +5310,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.759193056875047</v>
+        <v>-1.443027093329874</v>
       </c>
       <c r="O4" s="5">
         <v>17</v>
       </c>
       <c r="P4" s="4">
-        <v>1.095580781017937</v>
+        <v>1.124970998570321</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.758755288938356</v>
+        <v>0.6684221564968781</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -5369,16 +5369,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2731735028599976</v>
+        <v>-0.2530031427886428</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2559615250077899</v>
+        <v>0.254967890846659</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2423167143081254</v>
+        <v>0.2403970296448046</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -5428,16 +5428,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.362459120850256</v>
+        <v>-0.8650788901722848</v>
       </c>
       <c r="O6" s="5">
         <v>23</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9500835352267866</v>
+        <v>0.9309078661259776</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6368527338273978</v>
+        <v>0.4817413016269101</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -5781,22 +5781,22 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.001329344307297298</v>
+        <v>0.2297797721621393</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4816403029912305</v>
+        <v>0.4359941751336114</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4816403029912305</v>
+        <v>0.3957745735218324</v>
       </c>
       <c r="R3" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -5840,22 +5840,22 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2066585483373972</v>
+        <v>-0.3427481594116983</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>1.068717558260873</v>
+        <v>1.03186834202489</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6951919680483877</v>
+        <v>0.7660486989533515</v>
       </c>
       <c r="R4" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -5899,16 +5899,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2460647639603535</v>
+        <v>0.2089142084296398</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2398372154915379</v>
+        <v>0.2332499456814346</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2536515882646149</v>
+        <v>0.2486451135545483</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.07607321839610064</v>
+        <v>0.2468791326900792</v>
       </c>
       <c r="O6" s="5">
         <v>23</v>
@@ -5967,7 +5967,7 @@
         <v>0.6386025847402269</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6543126779444743</v>
+        <v>0.6468863338447363</v>
       </c>
       <c r="R6" s="5">
         <v>23</v>
@@ -6307,16 +6307,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9941982107411563</v>
+        <v>-0.5656867891448272</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.720929912180503</v>
+        <v>0.66071434006189</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5452396056620286</v>
+        <v>0.4453975205395015</v>
       </c>
       <c r="R3" s="5">
         <v>37</v>
@@ -6366,16 +6366,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.583444009756338</v>
+        <v>-1.379840201952902</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>1.105188317065542</v>
+        <v>1.131864587332519</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7114900949271343</v>
+        <v>0.6605891429762754</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -6425,16 +6425,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1055693997716187</v>
+        <v>-0.07921115892530395</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2239089522122202</v>
+        <v>0.2198440750565006</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2102948854656859</v>
+        <v>0.2046878934174274</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -6484,16 +6484,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.210418963544619</v>
+        <v>-0.9394915640295736</v>
       </c>
       <c r="O6" s="5">
         <v>21</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9613098431468359</v>
+        <v>0.9126068640656064</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6502418405148385</v>
+        <v>0.5336739760151535</v>
       </c>
       <c r="R6" s="5">
         <v>17</v>
@@ -6779,13 +6779,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>78.2051282051282</v>
+        <v>77.56410256410257</v>
       </c>
       <c r="C3" s="3">
         <v>13.46153846153846</v>
       </c>
       <c r="D3" s="3">
-        <v>8.333333333333332</v>
+        <v>8.974358974358974</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -6794,16 +6794,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>8.333333333333332</v>
+        <v>8.974358974358974</v>
       </c>
       <c r="H3" s="4">
-        <v>0.8790829826918648</v>
+        <v>0.8601815773545241</v>
       </c>
       <c r="I3" s="4">
-        <v>0.5219263786665772</v>
+        <v>0.4122810087535696</v>
       </c>
       <c r="J3" s="4">
-        <v>0.8422255053172096</v>
+        <v>0.7835296491984292</v>
       </c>
       <c r="K3" s="4">
         <v>88.99071166928289</v>
@@ -6829,13 +6829,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>69.23076923076923</v>
+        <v>69.87179487179486</v>
       </c>
       <c r="C4" s="3">
         <v>24.35897435897436</v>
       </c>
       <c r="D4" s="3">
-        <v>6.41025641025641</v>
+        <v>5.769230769230769</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -6844,16 +6844,16 @@
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <v>6.41025641025641</v>
+        <v>5.769230769230769</v>
       </c>
       <c r="H4" s="4">
-        <v>0.962435634802683</v>
+        <v>0.9489225666530752</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5110586264145832</v>
+        <v>0.4369060867388601</v>
       </c>
       <c r="J4" s="4">
-        <v>0.9137926266475802</v>
+        <v>0.8625513408546212</v>
       </c>
       <c r="K4" s="4">
         <v>81.82779522065235</v>
@@ -6897,13 +6897,13 @@
         <v>5.769230769230769</v>
       </c>
       <c r="H5" s="4">
-        <v>0.8180474654000987</v>
+        <v>0.8016478741066329</v>
       </c>
       <c r="I5" s="4">
-        <v>0.5731154904668406</v>
+        <v>0.4437433361331961</v>
       </c>
       <c r="J5" s="4">
-        <v>0.7345134391013389</v>
+        <v>0.6897457471998515</v>
       </c>
       <c r="K5" s="4">
         <v>87.41910866910877</v>
@@ -6947,13 +6947,13 @@
         <v>5.769230769230769</v>
       </c>
       <c r="H6" s="4">
-        <v>0.8119164069414717</v>
+        <v>0.7831249764941066</v>
       </c>
       <c r="I6" s="4">
-        <v>0.5324822294927277</v>
+        <v>0.4167657713933465</v>
       </c>
       <c r="J6" s="4">
-        <v>0.7224479058674282</v>
+        <v>0.6551678191274102</v>
       </c>
       <c r="K6" s="4">
         <v>86.04330193615884</v>
@@ -6979,13 +6979,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>53.2051282051282</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C7" s="3">
         <v>17.30769230769231</v>
       </c>
       <c r="D7" s="3">
-        <v>29.48717948717949</v>
+        <v>16.02564102564103</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -6994,16 +6994,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <v>29.48717948717949</v>
+        <v>16.02564102564103</v>
       </c>
       <c r="H7" s="4">
-        <v>1.573615709228179</v>
+        <v>1.564912008668006</v>
       </c>
       <c r="I7" s="4">
-        <v>0.4883602039838482</v>
+        <v>0.730990596347965</v>
       </c>
       <c r="J7" s="4">
-        <v>1.507181508138613</v>
+        <v>1.49232334988105</v>
       </c>
       <c r="K7" s="4">
         <v>89.93764172335555</v>
@@ -7029,13 +7029,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>75</v>
+        <v>74.35897435897436</v>
       </c>
       <c r="C8" s="3">
         <v>16.02564102564103</v>
       </c>
       <c r="D8" s="3">
-        <v>8.974358974358974</v>
+        <v>9.615384615384617</v>
       </c>
       <c r="E8" s="3">
         <v>0.641025641025641</v>
@@ -7044,16 +7044,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <v>8.333333333333332</v>
+        <v>8.974358974358974</v>
       </c>
       <c r="H8" s="4">
-        <v>1.071086610348392</v>
+        <v>1.045558884000412</v>
       </c>
       <c r="I8" s="4">
-        <v>0.7596910088866733</v>
+        <v>0.6301920521643463</v>
       </c>
       <c r="J8" s="4">
-        <v>1.027021922984266</v>
+        <v>0.9741757714152514</v>
       </c>
       <c r="K8" s="4">
         <v>88.23805163090869</v>
@@ -7079,13 +7079,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>72.43589743589743</v>
+        <v>73.07692307692307</v>
       </c>
       <c r="C9" s="3">
         <v>20.51282051282051</v>
       </c>
       <c r="D9" s="3">
-        <v>7.051282051282051</v>
+        <v>6.41025641025641</v>
       </c>
       <c r="E9" s="3">
         <v>0.641025641025641</v>
@@ -7094,16 +7094,16 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>6.41025641025641</v>
+        <v>5.769230769230769</v>
       </c>
       <c r="H9" s="4">
-        <v>0.9756149704347047</v>
+        <v>0.942819451125242</v>
       </c>
       <c r="I9" s="4">
-        <v>0.5210440562759608</v>
+        <v>0.4497116630863865</v>
       </c>
       <c r="J9" s="4">
-        <v>0.9126978373090483</v>
+        <v>0.853415905101102</v>
       </c>
       <c r="K9" s="4">
         <v>85.76399790685457</v>
@@ -7129,13 +7129,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>82.69230769230769</v>
+        <v>80.76923076923077</v>
       </c>
       <c r="C10" s="3">
         <v>12.82051282051282</v>
       </c>
       <c r="D10" s="3">
-        <v>4.487179487179487</v>
+        <v>6.41025641025641</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -7144,16 +7144,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>4.487179487179487</v>
+        <v>6.41025641025641</v>
       </c>
       <c r="H10" s="4">
-        <v>0.6279315781267164</v>
+        <v>0.6068048204848543</v>
       </c>
       <c r="I10" s="4">
-        <v>0.4647664972647436</v>
+        <v>0.3838613335441668</v>
       </c>
       <c r="J10" s="4">
-        <v>0.5536020073615655</v>
+        <v>0.5325558273305888</v>
       </c>
       <c r="K10" s="4">
         <v>91.11111111111083</v>
@@ -7179,13 +7179,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>70.51282051282051</v>
+        <v>69.87179487179486</v>
       </c>
       <c r="C11" s="3">
         <v>23.07692307692308</v>
       </c>
       <c r="D11" s="3">
-        <v>6.41025641025641</v>
+        <v>7.051282051282051</v>
       </c>
       <c r="E11" s="3">
         <v>1.282051282051282</v>
@@ -7194,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="3">
-        <v>5.128205128205128</v>
+        <v>5.769230769230769</v>
       </c>
       <c r="H11" s="4">
-        <v>0.7830866820030957</v>
+        <v>0.7383241460793215</v>
       </c>
       <c r="I11" s="4">
-        <v>0.5577995553459991</v>
+        <v>0.4659194961773502</v>
       </c>
       <c r="J11" s="4">
-        <v>0.6789002386461876</v>
+        <v>0.6310525812714332</v>
       </c>
       <c r="K11" s="4">
         <v>86.77895517181216</v>
@@ -7229,13 +7229,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>75.64102564102564</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3">
         <v>18.58974358974359</v>
       </c>
       <c r="D12" s="3">
-        <v>5.769230769230769</v>
+        <v>6.41025641025641</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -7244,16 +7244,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>5.769230769230769</v>
+        <v>6.41025641025641</v>
       </c>
       <c r="H12" s="4">
-        <v>0.7120351991271772</v>
+        <v>0.7040168431404965</v>
       </c>
       <c r="I12" s="4">
-        <v>0.5034852071732312</v>
+        <v>0.4201137976420314</v>
       </c>
       <c r="J12" s="4">
-        <v>0.6691275931969591</v>
+        <v>0.6470148422447378</v>
       </c>
       <c r="K12" s="4">
         <v>88.16413744985213</v>
@@ -7297,13 +7297,13 @@
         <v>5.769230769230769</v>
       </c>
       <c r="H13" s="4">
-        <v>0.7992655521217151</v>
+        <v>0.7828310712718051</v>
       </c>
       <c r="I13" s="4">
-        <v>0.5440184639164097</v>
+        <v>0.4402511585692631</v>
       </c>
       <c r="J13" s="4">
-        <v>0.7540911187459863</v>
+        <v>0.7171521428352161</v>
       </c>
       <c r="K13" s="4">
         <v>90.10116867259715</v>
@@ -7347,13 +7347,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.5493859550487743</v>
+        <v>0.5340322426232663</v>
       </c>
       <c r="I14" s="4">
-        <v>0.5069837464798006</v>
+        <v>0.4886792097596033</v>
       </c>
       <c r="J14" s="4">
-        <v>0.5351729356805436</v>
+        <v>0.5205407300147273</v>
       </c>
       <c r="K14" s="4">
         <v>79.76775085034011</v>
@@ -7397,13 +7397,13 @@
         <v>7.8125</v>
       </c>
       <c r="H15" s="4">
-        <v>0.757551930175315</v>
+        <v>0.7409124665425035</v>
       </c>
       <c r="I15" s="4">
-        <v>0.5523639701098846</v>
+        <v>0.4784429800904496</v>
       </c>
       <c r="J15" s="4">
-        <v>0.7602691727515468</v>
+        <v>0.7253436657928705</v>
       </c>
       <c r="K15" s="4">
         <v>89.85544217687074</v>
@@ -7447,13 +7447,13 @@
         <v>0.78125</v>
       </c>
       <c r="H16" s="4">
-        <v>0.5960501796931869</v>
+        <v>0.5722840334150994</v>
       </c>
       <c r="I16" s="4">
-        <v>0.5142059453780158</v>
+        <v>0.4917934770104886</v>
       </c>
       <c r="J16" s="4">
-        <v>0.5483261588477241</v>
+        <v>0.5300068247438052</v>
       </c>
       <c r="K16" s="4">
         <v>80.33827593537414</v>
@@ -7497,13 +7497,13 @@
         <v>7.8125</v>
       </c>
       <c r="H17" s="4">
-        <v>0.7645917140861889</v>
+        <v>0.7415887814644793</v>
       </c>
       <c r="I17" s="4">
-        <v>0.5418679545001367</v>
+        <v>0.476220421050153</v>
       </c>
       <c r="J17" s="4">
-        <v>0.7525714081428601</v>
+        <v>0.7191782172428077</v>
       </c>
       <c r="K17" s="4">
         <v>89.64232568027199</v>
@@ -8386,13 +8386,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" s="5">
         <v>21</v>
       </c>
       <c r="D3" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5">
         <v>0</v>
@@ -8401,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="5">
         <v>0</v>
@@ -8430,13 +8430,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C4" s="5">
         <v>38</v>
       </c>
       <c r="D4" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -8445,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -8562,13 +8562,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C7" s="5">
         <v>27</v>
       </c>
       <c r="D7" s="5">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5">
         <v>0</v>
@@ -8577,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -8606,13 +8606,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="5">
         <v>25</v>
       </c>
       <c r="D8" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -8621,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -8650,13 +8650,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="5">
         <v>32</v>
       </c>
       <c r="D9" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" s="5">
         <v>1</v>
@@ -8665,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5">
         <v>1</v>
@@ -8694,13 +8694,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C10" s="5">
         <v>20</v>
       </c>
       <c r="D10" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" s="5">
         <v>0</v>
@@ -8709,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
@@ -8738,13 +8738,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="5">
         <v>36</v>
       </c>
       <c r="D11" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="5">
         <v>2</v>
@@ -8753,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="5">
         <v>2</v>
@@ -8782,13 +8782,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C12" s="5">
         <v>29</v>
       </c>
       <c r="D12" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="5">
         <v>0</v>
@@ -8797,7 +8797,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" s="5">
         <v>0</v>
@@ -9200,22 +9200,22 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.401307065988658</v>
+        <v>-0.9406176852426142</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8521802323364682</v>
+        <v>0.7976912854621332</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6182657061123471</v>
+        <v>0.4720840017701751</v>
       </c>
       <c r="R3" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S3" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -9259,16 +9259,16 @@
         <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>-2.597122091525047</v>
+        <v>-1.942520594791858</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>1.524524287593002</v>
+        <v>1.590217599756475</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8319610152332079</v>
+        <v>0.6171332005463531</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -9318,16 +9318,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2845348969211854</v>
+        <v>-0.2632744795955659</v>
       </c>
       <c r="O5" s="5">
         <v>54</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2439679496817426</v>
+        <v>0.2440099742693097</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2379182856988666</v>
+        <v>0.237174443888728</v>
       </c>
       <c r="R5" s="5">
         <v>54</v>
@@ -9377,16 +9377,16 @@
         <v>13</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.99728656241946</v>
+        <v>-2.354364710641676</v>
       </c>
       <c r="O6" s="5">
         <v>21</v>
       </c>
       <c r="P6" s="4">
-        <v>1.43122808273959</v>
+        <v>1.322443604609058</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.972272373045565</v>
+        <v>0.6610895588267286</v>
       </c>
       <c r="R6" s="5">
         <v>17</v>
@@ -9722,16 +9722,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.483376115875561</v>
+        <v>-1.018373920873273</v>
       </c>
       <c r="O3" s="5">
         <v>37</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9113886362963182</v>
+        <v>0.8453954269283713</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6578638558637135</v>
+        <v>0.5255186454305658</v>
       </c>
       <c r="R3" s="5">
         <v>34</v>
@@ -9781,16 +9781,16 @@
         <v>8</v>
       </c>
       <c r="N4" s="4">
-        <v>-2.911728979478669</v>
+        <v>-2.115180111126392</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>1.617571489226455</v>
+        <v>1.693199192684135</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.8878847694938617</v>
+        <v>0.6267244620921701</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -9840,16 +9840,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2152230490005009</v>
+        <v>-0.1590198768535629</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2534657981742538</v>
+        <v>0.2491100184371524</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2307650599240716</v>
+        <v>0.2226666506156272</v>
       </c>
       <c r="R5" s="5">
         <v>44</v>
@@ -9899,22 +9899,22 @@
         <v>17</v>
       </c>
       <c r="N6" s="4">
-        <v>-3.470290800249801</v>
+        <v>-3.061057039943989</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>1.58531873852928</v>
+        <v>1.52940364318935</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6108088284333318</v>
+        <v>0.5994919946948786</v>
       </c>
       <c r="R6" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S6" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -10244,16 +10244,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9084255821393239</v>
+        <v>-0.3582634453196079</v>
       </c>
       <c r="O3" s="5">
         <v>38</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7168079096587845</v>
+        <v>0.6408748688558262</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5405945507806673</v>
+        <v>0.4190872467991929</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -10303,16 +10303,16 @@
         <v>6</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.986312426883939</v>
+        <v>-1.620142749146908</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>1.319827427960782</v>
+        <v>1.367500097380668</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.7401518059744245</v>
+        <v>0.618868599506944</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -10362,16 +10362,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3929330804574803</v>
+        <v>-0.3509275762444304</v>
       </c>
       <c r="O5" s="5">
         <v>38</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4460148744342713</v>
+        <v>0.4558206756281444</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2945937045630452</v>
+        <v>0.2935686468755241</v>
       </c>
       <c r="R5" s="5">
         <v>38</v>
@@ -10421,16 +10421,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.866638202207014</v>
+        <v>-0.977504881171626</v>
       </c>
       <c r="O6" s="5">
         <v>16</v>
       </c>
       <c r="P6" s="4">
-        <v>1.158559396743802</v>
+        <v>1.100018804232301</v>
       </c>
       <c r="Q6" s="4">
-        <v>1.034125697318359</v>
+        <v>0.402606898378508</v>
       </c>
       <c r="R6" s="5">
         <v>12</v>
@@ -10770,16 +10770,16 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8397553997288923</v>
+        <v>-0.3373848334449576</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7017592804932065</v>
+        <v>0.6346285746334616</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5256522590776662</v>
+        <v>0.4123457743954606</v>
       </c>
       <c r="R3" s="5">
         <v>37</v>
@@ -10829,16 +10829,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.706633971399181</v>
+        <v>-1.445010013201681</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>1.254133070280208</v>
+        <v>1.282813444977364</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6515910635160533</v>
+        <v>0.5912163039320149</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -10888,16 +10888,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2000862948302827</v>
+        <v>-0.1379774944143719</v>
       </c>
       <c r="O5" s="5">
         <v>39</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4101215667861376</v>
+        <v>0.4220651132602922</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2413326879744531</v>
+        <v>0.2320245787212536</v>
       </c>
       <c r="R5" s="5">
         <v>39</v>
@@ -10947,16 +10947,16 @@
         <v>7</v>
       </c>
       <c r="N6" s="4">
-        <v>-2.311282611897588</v>
+        <v>-1.513787108255201</v>
       </c>
       <c r="O6" s="5">
         <v>17</v>
       </c>
       <c r="P6" s="4">
-        <v>1.271585996812759</v>
+        <v>1.134997496418085</v>
       </c>
       <c r="Q6" s="4">
-        <v>1.025789637393418</v>
+        <v>0.4841409490915024</v>
       </c>
       <c r="R6" s="5">
         <v>13</v>
@@ -11296,22 +11296,22 @@
         <v>3</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3191753940831404</v>
+        <v>-0.004406889605888864</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5629153918044902</v>
+        <v>0.4878603763154388</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4701993036948567</v>
+        <v>0.3264838864868924</v>
       </c>
       <c r="R3" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -11355,16 +11355,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-1.010799274678448</v>
+        <v>-0.7386585666790779</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>1.262441090018521</v>
+        <v>1.340195578018341</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6856646566339545</v>
+        <v>0.6467874126340446</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -11414,22 +11414,22 @@
         <v>24</v>
       </c>
       <c r="N5" s="4">
-        <v>2.908831908808073</v>
+        <v>1.609264725298999</v>
       </c>
       <c r="O5" s="5">
         <v>48</v>
       </c>
       <c r="P5" s="4">
-        <v>2.88686260616791</v>
+        <v>2.874897671819261</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1482415821984281</v>
+        <v>1.490135961635436</v>
       </c>
       <c r="R5" s="5">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="S5" s="5">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -11473,16 +11473,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6212069327064254</v>
+        <v>-0.3154729431626038</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8629986843870938</v>
+        <v>0.8687209340414483</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4925315458600987</v>
+        <v>0.3864646742626974</v>
       </c>
       <c r="R6" s="5">
         <v>16</v>
